--- a/nando/Nando_final/metrics/net_3_Urban_HPK11/trafo_loading_compare.xlsx
+++ b/nando/Nando_final/metrics/net_3_Urban_HPK11/trafo_loading_compare.xlsx
@@ -479,16 +479,16 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="E2" t="n">
-        <v>4.694722200229464</v>
+        <v>4.67376308155988</v>
       </c>
       <c r="F2" t="n">
-        <v>4.854389740539265</v>
+        <v>4.795306402110056</v>
       </c>
       <c r="G2" t="n">
-        <v>4.576152740522034</v>
+        <v>4.534942738925516</v>
       </c>
       <c r="H2" t="n">
         <v>11.06031860826563</v>
@@ -509,16 +509,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>9.157824910973813</v>
+        <v>10.33870494468933</v>
       </c>
       <c r="F3" t="n">
-        <v>9.242067132071332</v>
+        <v>10.35271820963854</v>
       </c>
       <c r="G3" t="n">
-        <v>9.157824910973813</v>
+        <v>10.33870494468933</v>
       </c>
       <c r="H3" t="n">
         <v>10.87717908040791</v>
@@ -527,1291 +527,1291 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TUILERIES_PROVENCE</t>
+          <t>mv_f0_lv_HIGHMOUNT_ORMOND</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mv_f0_lv_tuileries_provence</t>
+          <t>mv_f0_lv_highmount_ormond</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>8.855289185453033</v>
+        <v>8.703654914963598</v>
       </c>
       <c r="F4" t="n">
-        <v>8.862297307856151</v>
+        <v>8.714150178849192</v>
       </c>
       <c r="G4" t="n">
-        <v>8.855289185453033</v>
+        <v>8.703654914963598</v>
       </c>
       <c r="H4" t="n">
-        <v>9.41812697629026</v>
+        <v>9.131211298107832</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mv_f0_lv_CORAL_CLAUD</t>
+          <t>mv_f0_lv_TANGERINE_NORWEGIAN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mv_f0_lv_coral_claud</t>
+          <t>mv_f0_lv_tangerine_norwegian</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>8.466473378966908</v>
+        <v>8.662144647756186</v>
       </c>
       <c r="F5" t="n">
-        <v>8.655337902557131</v>
+        <v>8.709430644467428</v>
       </c>
       <c r="G5" t="n">
-        <v>8.466473378966908</v>
+        <v>8.662144647756186</v>
       </c>
       <c r="H5" t="n">
-        <v>10.91457897047595</v>
+        <v>9.568473645492205</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TANGERINE_NORWEGIAN</t>
+          <t>mv_f0_lv_TUILERIES_PROVENCE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mv_f0_lv_tangerine_norwegian</t>
+          <t>mv_f0_lv_tuileries_provence</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>8.087680798160633</v>
+        <v>8.566107564361307</v>
       </c>
       <c r="F6" t="n">
-        <v>8.25530396552525</v>
+        <v>8.566469115959013</v>
       </c>
       <c r="G6" t="n">
-        <v>8.087680798160633</v>
+        <v>8.566107564361307</v>
       </c>
       <c r="H6" t="n">
-        <v>9.568473645492205</v>
+        <v>8.644811506267644</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mv_f0_lv_JESSICA_GERALDINE</t>
+          <t>mv_f0_lv_MEREDITH_HARVEY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mv_f0_lv_jessica_geraldine</t>
+          <t>mv_f0_lv_meredith_harvey</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>7.16778916989677</v>
+        <v>7.641333227445244</v>
       </c>
       <c r="F7" t="n">
-        <v>7.331112044486524</v>
+        <v>7.729689662995275</v>
       </c>
       <c r="G7" t="n">
-        <v>7.16778916989677</v>
+        <v>7.641333227445244</v>
       </c>
       <c r="H7" t="n">
-        <v>8.955805805452631</v>
+        <v>8.806721057035574</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HIGHMOUNT_ORMOND</t>
+          <t>mv_f0_lv_VON_NIDA_DULWICH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mv_f0_lv_highmount_ormond</t>
+          <t>mv_f0_lv_von_nida_dulwich</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>6.905855998292592</v>
+        <v>7.578714805990799</v>
       </c>
       <c r="F8" t="n">
-        <v>7.206082620315183</v>
+        <v>7.737742686695906</v>
       </c>
       <c r="G8" t="n">
-        <v>6.905855998292592</v>
+        <v>7.578714805990799</v>
       </c>
       <c r="H8" t="n">
-        <v>9.131211298107832</v>
+        <v>9.139401762100775</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mv_f0_lv_MEREDITH_HARVEY</t>
+          <t>mv_f0_lv_EDEYS_PIONEER</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mv_f0_lv_meredith_harvey</t>
+          <t>mv_f0_lv_edeys_pioneer</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>6.905417428897577</v>
+        <v>7.560760690963598</v>
       </c>
       <c r="F9" t="n">
-        <v>7.028030135199645</v>
+        <v>8.331386909907119</v>
       </c>
       <c r="G9" t="n">
-        <v>6.905417428897577</v>
+        <v>7.560760690963598</v>
       </c>
       <c r="H9" t="n">
-        <v>8.806721057035574</v>
+        <v>11.06031860826563</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LEOPOLD_HAZEL</t>
+          <t>mv_f0_lv_CORAL_CLAUD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mv_f0_lv_leopold_hazel</t>
+          <t>mv_f0_lv_coral_claud</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>6.643220141154424</v>
+        <v>6.742923501014221</v>
       </c>
       <c r="F10" t="n">
-        <v>6.68876143710408</v>
+        <v>6.743010711564586</v>
       </c>
       <c r="G10" t="n">
-        <v>6.643220141154424</v>
+        <v>6.742923501014221</v>
       </c>
       <c r="H10" t="n">
-        <v>7.91731378144539</v>
+        <v>6.777218044965949</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mv_f0_lv_VON_NIDA_DULWICH</t>
+          <t>mv_f0_lv_GERALDINE_PAULINE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mv_f0_lv_von_nida_dulwich</t>
+          <t>mv_f0_lv_geraldine_pauline</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>6.387076102458002</v>
+        <v>6.42105124386983</v>
       </c>
       <c r="F11" t="n">
-        <v>6.623997785653168</v>
+        <v>6.52697163988903</v>
       </c>
       <c r="G11" t="n">
-        <v>6.387076102458002</v>
+        <v>6.42105124386983</v>
       </c>
       <c r="H11" t="n">
-        <v>9.139401762100775</v>
+        <v>7.592144626787441</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mv_f0_lv_PARKWAY_REDWOOD</t>
+          <t>mv_f0_lv_TOOMAH_STRATHARD</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mv_f0_lv_parkway_redwood</t>
+          <t>mv_f0_lv_toomah_strathard</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>6.010272611284956</v>
+        <v>6.170552281710302</v>
       </c>
       <c r="F12" t="n">
-        <v>6.25266584013688</v>
+        <v>6.170699426104486</v>
       </c>
       <c r="G12" t="n">
-        <v>6.010272611284956</v>
+        <v>6.170552281710302</v>
       </c>
       <c r="H12" t="n">
-        <v>7.74850836887034</v>
+        <v>6.213166199695049</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GOLDEN_CHERRYWOOD</t>
+          <t>mv_f0_lv_LEOPOLD_HAZEL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mv_f0_lv_golden_cherrywood</t>
+          <t>mv_f0_lv_leopold_hazel</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>5.935034941966206</v>
+        <v>6.098715924784443</v>
       </c>
       <c r="F13" t="n">
-        <v>5.97459686579541</v>
+        <v>6.106011542548398</v>
       </c>
       <c r="G13" t="n">
-        <v>5.935034941966206</v>
+        <v>6.098715924784443</v>
       </c>
       <c r="H13" t="n">
-        <v>6.854716468633505</v>
+        <v>6.397113355260814</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GERALDINE_PAULINE</t>
+          <t>mv_f0_lv_NORWEGIAN_GLASSCOCKS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mv_f0_lv_geraldine_pauline</t>
+          <t>mv_f0_lv_norwegian_glasscocks</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>5.877883265661302</v>
+        <v>6.016597126595563</v>
       </c>
       <c r="F14" t="n">
-        <v>5.963054332852492</v>
+        <v>6.028980183750392</v>
       </c>
       <c r="G14" t="n">
-        <v>5.877883265661302</v>
+        <v>6.016597126595563</v>
       </c>
       <c r="H14" t="n">
-        <v>7.592144626787441</v>
+        <v>6.402810891623311</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mv_f0_lv_MALABAR_BYRON</t>
+          <t>mv_f0_lv_ORMOND_TANGERINE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mv_f0_lv_malabar_byron</t>
+          <t>mv_f0_lv_ormond_tangerine</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.820939870460984</v>
+        <v>5.987472229624299</v>
       </c>
       <c r="F15" t="n">
-        <v>5.898066241581105</v>
+        <v>6.055097491211796</v>
       </c>
       <c r="G15" t="n">
-        <v>5.820939870460984</v>
+        <v>5.987472229624299</v>
       </c>
       <c r="H15" t="n">
-        <v>6.750472035715728</v>
+        <v>6.88990335029624</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFIELD_JANET</t>
+          <t>mv_f0_lv_JESSICA_GERALDINE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfield_janet</t>
+          <t>mv_f0_lv_jessica_geraldine</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>5.553122303520282</v>
+        <v>5.640198490131667</v>
       </c>
       <c r="F16" t="n">
-        <v>5.687458197855448</v>
+        <v>5.640297439787684</v>
       </c>
       <c r="G16" t="n">
-        <v>5.553122303520282</v>
+        <v>5.640198490131667</v>
       </c>
       <c r="H16" t="n">
-        <v>7.290221048453379</v>
+        <v>5.673608087435007</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mv_f0_lv_NIMBUS_AMBER</t>
+          <t>mv_f0_lv_SPRINGFIELD_JANET</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mv_f0_lv_nimbus_amber</t>
+          <t>mv_f0_lv_springfield_janet</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>5.369024287371707</v>
+        <v>5.557826824733615</v>
       </c>
       <c r="F17" t="n">
-        <v>5.40996945892611</v>
+        <v>5.821565834043804</v>
       </c>
       <c r="G17" t="n">
-        <v>5.369024287371707</v>
+        <v>5.557826824733615</v>
       </c>
       <c r="H17" t="n">
-        <v>6.023638720901634</v>
+        <v>7.290221048453379</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mv_f0_lv_EDEYS_PIONEER</t>
+          <t>mv_f0_lv_GREENVIEW_SNOWDONIA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mv_f0_lv_edeys_pioneer</t>
+          <t>mv_f0_lv_greenview_snowdonia</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.251038838188268</v>
+        <v>5.334215010386488</v>
       </c>
       <c r="F18" t="n">
-        <v>6.253114072278294</v>
+        <v>5.391198958847043</v>
       </c>
       <c r="G18" t="n">
-        <v>5.251038838188268</v>
+        <v>5.334215010386488</v>
       </c>
       <c r="H18" t="n">
-        <v>11.06031860826563</v>
+        <v>6.115992751717688</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TOOMAH_STRATHARD</t>
+          <t>mv_f0_lv_GOLDEN_CHERRYWOOD</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mv_f0_lv_toomah_strathard</t>
+          <t>mv_f0_lv_golden_cherrywood</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>5.205666921438486</v>
+        <v>5.297386540121654</v>
       </c>
       <c r="F19" t="n">
-        <v>5.297322086745921</v>
+        <v>5.302066238367832</v>
       </c>
       <c r="G19" t="n">
-        <v>5.205666921438486</v>
+        <v>5.297386540121654</v>
       </c>
       <c r="H19" t="n">
-        <v>6.213166199695049</v>
+        <v>5.520102144824037</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mv_f0_lv_OAKGROVE_OXENFORD</t>
+          <t>mv_f0_lv_NIMBUS_AMBER</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mv_f0_lv_oakgrove_oxenford</t>
+          <t>mv_f0_lv_nimbus_amber</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>5.182411644255437</v>
+        <v>5.142212488996437</v>
       </c>
       <c r="F20" t="n">
-        <v>5.338598640091965</v>
+        <v>5.217208207871479</v>
       </c>
       <c r="G20" t="n">
-        <v>5.182411644255437</v>
+        <v>5.142212488996437</v>
       </c>
       <c r="H20" t="n">
-        <v>6.788283186385279</v>
+        <v>6.023638720901634</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFLD_KATHERINE</t>
+          <t>mv_f0_lv_MALABAR_BYRON</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfld_katherine</t>
+          <t>mv_f0_lv_malabar_byron</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.145128733822292</v>
+        <v>5.05004964324441</v>
       </c>
       <c r="F21" t="n">
-        <v>5.252519360370323</v>
+        <v>5.108520282724255</v>
       </c>
       <c r="G21" t="n">
-        <v>5.145128733822292</v>
+        <v>5.05004964324441</v>
       </c>
       <c r="H21" t="n">
-        <v>6.154243510425427</v>
+        <v>5.820749377104562</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LESLEY_CARMEN</t>
+          <t>mv_f0_lv_RALEIGH_LOWDEN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mv_f0_lv_lesley_carmen</t>
+          <t>mv_f0_lv_raleigh_lowden</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>5.043270431521998</v>
+        <v>5.032876280621943</v>
       </c>
       <c r="F22" t="n">
-        <v>5.09167367327821</v>
+        <v>5.049865737252153</v>
       </c>
       <c r="G22" t="n">
-        <v>5.043270431521998</v>
+        <v>5.032876280621943</v>
       </c>
       <c r="H22" t="n">
-        <v>5.826279491014663</v>
+        <v>5.446760694711514</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mv_f0_lv_NORWEGIAN_GLASSCOCKS</t>
+          <t>mv_f0_lv_PARKWAY_REDWOOD</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mv_f0_lv_norwegian_glasscocks</t>
+          <t>mv_f0_lv_parkway_redwood</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>4.848136895854831</v>
+        <v>4.777956465714333</v>
       </c>
       <c r="F23" t="n">
-        <v>4.994536880839111</v>
+        <v>5.047832570725505</v>
       </c>
       <c r="G23" t="n">
-        <v>4.848136895854831</v>
+        <v>4.777956465714333</v>
       </c>
       <c r="H23" t="n">
-        <v>6.402810891623311</v>
+        <v>6.406374616502347</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GREENVIEW_SNOWDONIA</t>
+          <t>mv_f0_lv_LESLEY_CARMEN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mv_f0_lv_greenview_snowdonia</t>
+          <t>mv_f0_lv_lesley_carmen</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.772494003296372</v>
+        <v>4.345684515766015</v>
       </c>
       <c r="F24" t="n">
-        <v>4.84762019528101</v>
+        <v>4.345751129176762</v>
       </c>
       <c r="G24" t="n">
-        <v>4.772494003296372</v>
+        <v>4.345684515766015</v>
       </c>
       <c r="H24" t="n">
-        <v>6.115992751717688</v>
+        <v>4.369746231677226</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mv_f0_lv_RALEIGH_LOWDEN</t>
+          <t>mv_f0_lv_HALLAM_EDEYS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mv_f0_lv_raleigh_lowden</t>
+          <t>mv_f0_lv_hallam_edeys</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>4.69683370680626</v>
+        <v>4.300457061557832</v>
       </c>
       <c r="F25" t="n">
-        <v>4.71913497054704</v>
+        <v>4.316161911813845</v>
       </c>
       <c r="G25" t="n">
-        <v>4.69683370680626</v>
+        <v>4.300457061557832</v>
       </c>
       <c r="H25" t="n">
-        <v>5.446760694711514</v>
+        <v>4.668319414469792</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_STRATHAIRD</t>
+          <t>mv_f0_lv_SPRINGFLD_KATHERINE</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_strathaird</t>
+          <t>mv_f0_lv_springfld_katherine</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>4.627682917901319</v>
+        <v>4.279093313526406</v>
       </c>
       <c r="F26" t="n">
-        <v>4.747490224855506</v>
+        <v>4.361576902013026</v>
       </c>
       <c r="G26" t="n">
-        <v>4.627682917901319</v>
+        <v>4.279093313526406</v>
       </c>
       <c r="H26" t="n">
-        <v>5.597906160455899</v>
+        <v>5.123316913236309</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mv_f0_lv_MICHELLE_SIMON</t>
+          <t>mv_f0_lv_ORMOND_STRATHAIRD</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mv_f0_lv_michelle_simon</t>
+          <t>mv_f0_lv_ormond_strathaird</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.611210014890348</v>
+        <v>4.028795177174223</v>
       </c>
       <c r="F27" t="n">
-        <v>4.722152495135219</v>
+        <v>4.197903758501883</v>
       </c>
       <c r="G27" t="n">
-        <v>4.611210014890348</v>
+        <v>4.028795177174223</v>
       </c>
       <c r="H27" t="n">
-        <v>6.06304648491475</v>
+        <v>5.208288876191713</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HALLAM_EDEYS</t>
+          <t>mv_f0_lv_OAKGROVE_OXENFORD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hallam_edeys</t>
+          <t>mv_f0_lv_oakgrove_oxenford</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>4.365389622975987</v>
+        <v>3.952848069203633</v>
       </c>
       <c r="F28" t="n">
-        <v>4.455098364948241</v>
+        <v>3.968152842430217</v>
       </c>
       <c r="G28" t="n">
-        <v>4.365389622975987</v>
+        <v>3.952848069203633</v>
       </c>
       <c r="H28" t="n">
-        <v>5.629819819323682</v>
+        <v>4.301027796758426</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_TANGERINE</t>
+          <t>mv_f0_lv_MICHELLE_SIMON</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_tangerine</t>
+          <t>mv_f0_lv_michelle_simon</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>4.354415338462381</v>
+        <v>3.898179694329004</v>
       </c>
       <c r="F29" t="n">
-        <v>4.789402061731736</v>
+        <v>3.96283720312712</v>
       </c>
       <c r="G29" t="n">
-        <v>4.354415338462381</v>
+        <v>3.898179694329004</v>
       </c>
       <c r="H29" t="n">
-        <v>6.88990335029624</v>
+        <v>4.611112909440639</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mv_f0_lv_EDEYS_MOLLISONS</t>
+          <t>mv_f0_lv_KERSHAW_ORMOND</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mv_f0_lv_edeys_mollisons</t>
+          <t>mv_f0_lv_kershaw_ormond</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.017217129624635</v>
+        <v>3.804851347164465</v>
       </c>
       <c r="F30" t="n">
-        <v>4.103842772373945</v>
+        <v>4.684273111958299</v>
       </c>
       <c r="G30" t="n">
-        <v>4.017217129624635</v>
+        <v>3.804851347164465</v>
       </c>
       <c r="H30" t="n">
-        <v>5.285746203960869</v>
+        <v>6.53716187369622</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HADLEY_CHESTERFIELD</t>
+          <t>mv_f0_lv_TIMMS_STRATHAIRD</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hadley_chesterfield</t>
+          <t>mv_f0_lv_timms_strathaird</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>3.993598914471955</v>
+        <v>3.530775127110449</v>
       </c>
       <c r="F31" t="n">
-        <v>4.097266528693918</v>
+        <v>3.878995877736294</v>
       </c>
       <c r="G31" t="n">
-        <v>3.993598914471955</v>
+        <v>3.530775127110449</v>
       </c>
       <c r="H31" t="n">
-        <v>4.955719120830651</v>
+        <v>5.137086436064401</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mv_f0_lv_BARINGA_PARK_CASPIAN</t>
+          <t>mv_f0_lv_HADLEY_CHESTERFIELD</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mv_f0_lv_baringa_park_caspian</t>
+          <t>mv_f0_lv_hadley_chesterfield</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>3.738446527599326</v>
+        <v>3.517246481454302</v>
       </c>
       <c r="F32" t="n">
-        <v>4.307284976627256</v>
+        <v>3.654962467080907</v>
       </c>
       <c r="G32" t="n">
-        <v>3.738446527599326</v>
+        <v>3.517246481454302</v>
       </c>
       <c r="H32" t="n">
-        <v>6.318794409014831</v>
+        <v>4.511091451491119</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mv_f0_lv_COMMUNITY_HARRINGTON</t>
+          <t>mv_f0_lv_EDEYS_MOLLISONS</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mv_f0_lv_community_harrington</t>
+          <t>mv_f0_lv_edeys_mollisons</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.643947482875385</v>
+        <v>3.291751593635354</v>
       </c>
       <c r="F33" t="n">
-        <v>3.721637584069288</v>
+        <v>3.300771747233533</v>
       </c>
       <c r="G33" t="n">
-        <v>3.643947482875385</v>
+        <v>3.291751593635354</v>
       </c>
       <c r="H33" t="n">
-        <v>4.902895107817287</v>
+        <v>3.53560723358288</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TIMMS_STRATHAIRD</t>
+          <t>mv_f0_lv_SHERWOOD_FLEET</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mv_f0_lv_timms_strathaird</t>
+          <t>mv_f0_lv_sherwood_fleet</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>3.423279689548466</v>
+        <v>3.268164578145162</v>
       </c>
       <c r="F34" t="n">
-        <v>3.635872794288951</v>
+        <v>3.31907653751956</v>
       </c>
       <c r="G34" t="n">
-        <v>3.423279689548466</v>
+        <v>3.268164578145162</v>
       </c>
       <c r="H34" t="n">
-        <v>5.137086436064401</v>
+        <v>3.847275406976813</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mv_f0_lv_KERSHAW_ORMOND</t>
+          <t>mv_f0_lv_LESLEY_AMY</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mv_f0_lv_kershaw_ormond</t>
+          <t>mv_f0_lv_lesley_amy</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>3.369743409817826</v>
+        <v>3.248770189155404</v>
       </c>
       <c r="F35" t="n">
-        <v>3.99068462033447</v>
+        <v>3.322072485391456</v>
       </c>
       <c r="G35" t="n">
-        <v>3.369743409817826</v>
+        <v>3.248770189155404</v>
       </c>
       <c r="H35" t="n">
-        <v>6.53716187369622</v>
+        <v>3.942785935554667</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SHERWOOD_FLEET</t>
+          <t>mv_f0_lv_COMMUNITY_HARRINGTON</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mv_f0_lv_sherwood_fleet</t>
+          <t>mv_f0_lv_community_harrington</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.183960783136286</v>
+        <v>3.171313186205175</v>
       </c>
       <c r="F36" t="n">
-        <v>3.244347527034806</v>
+        <v>3.183808790805393</v>
       </c>
       <c r="G36" t="n">
-        <v>3.183960783136286</v>
+        <v>3.171313186205175</v>
       </c>
       <c r="H36" t="n">
-        <v>3.847275406976813</v>
+        <v>3.453112922562173</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LESLEY_AMY</t>
+          <t>mv_f0_lv_CHISHOLM_KERSHAW</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mv_f0_lv_lesley_amy</t>
+          <t>mv_f0_lv_chisholm_kershaw</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>2.80503178085314</v>
+        <v>2.788889228499116</v>
       </c>
       <c r="F37" t="n">
-        <v>2.905379598067139</v>
+        <v>2.799097877410158</v>
       </c>
       <c r="G37" t="n">
-        <v>2.80503178085314</v>
+        <v>2.788889228499116</v>
       </c>
       <c r="H37" t="n">
-        <v>3.942785935554667</v>
+        <v>3.027731851336114</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>mv_f0_lv_CHISHOLM_KERSHAW</t>
+          <t>mv_f0_lv_HALLAM_RD_RETIREMENT</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>mv_f0_lv_chisholm_kershaw</t>
+          <t>mv_f0_lv_hallam_rd_retirement</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>2.745270200798126</v>
+        <v>2.365045981897813</v>
       </c>
       <c r="F38" t="n">
-        <v>2.796097458488374</v>
+        <v>2.461922019803509</v>
       </c>
       <c r="G38" t="n">
-        <v>2.745270200798126</v>
+        <v>2.365045981897813</v>
       </c>
       <c r="H38" t="n">
-        <v>3.410491074845837</v>
+        <v>3.048871643234385</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HALLAM_RD_RETIREMENT</t>
+          <t>mv_f0_lv_VIEWSIDE_NEESAN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hallam_rd_retirement</t>
+          <t>mv_f0_lv_viewside_neesan</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.533457417078604</v>
+        <v>2.043148938032417</v>
       </c>
       <c r="F39" t="n">
-        <v>2.594168983561753</v>
+        <v>2.104416910594919</v>
       </c>
       <c r="G39" t="n">
-        <v>2.533457417078604</v>
+        <v>2.043148938032417</v>
       </c>
       <c r="H39" t="n">
-        <v>3.048871643234385</v>
+        <v>2.547245110022317</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFIELD_HUNTNGTN</t>
+          <t>mv_f0_lv_BARINGA_PARK_CASPIAN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfield_huntngtn</t>
+          <t>mv_f0_lv_baringa_park_caspian</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>2.226241048598625</v>
+        <v>1.933007051943891</v>
       </c>
       <c r="F40" t="n">
-        <v>2.247728614075371</v>
+        <v>2.402135026462097</v>
       </c>
       <c r="G40" t="n">
-        <v>2.226241048598625</v>
+        <v>1.933007051943891</v>
       </c>
       <c r="H40" t="n">
-        <v>2.565559915455205</v>
+        <v>3.3590983612545</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>mv_f0_lv_VIEWSIDE_NEESAN</t>
+          <t>mv_f0_lv_SPRINGFIELD_HUNTNGTN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mv_f0_lv_viewside_neesan</t>
+          <t>mv_f0_lv_springfield_huntngtn</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>1.859266410711455</v>
+        <v>1.918467312718482</v>
       </c>
       <c r="F41" t="n">
-        <v>1.908841234296313</v>
+        <v>1.918942891756052</v>
       </c>
       <c r="G41" t="n">
-        <v>1.859266410711455</v>
+        <v>1.918467312718482</v>
       </c>
       <c r="H41" t="n">
-        <v>2.547245110022317</v>
+        <v>1.961187236077567</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_SCHOOL</t>
+          <t>mv_f0_lv_THE_PARKWAY_KARKALLA</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_school</t>
+          <t>mv_f0_lv_the_parkway_karkalla</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.840832962516165</v>
+        <v>1.756843051121447</v>
       </c>
       <c r="F42" t="n">
-        <v>1.869743209857475</v>
+        <v>2.441051062767997</v>
       </c>
       <c r="G42" t="n">
-        <v>1.840832962516165</v>
+        <v>-1.756843051121447</v>
       </c>
       <c r="H42" t="n">
-        <v>2.264758073634495</v>
+        <v>3.451609343200403</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SALLYS_RUN_ORMOND</t>
+          <t>mv_f0_lv_ORMOND_SCHOOL</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mv_f0_lv_sallys_run_ormond</t>
+          <t>mv_f0_lv_ormond_school</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>1.746511035450367</v>
+        <v>1.578680583191157</v>
       </c>
       <c r="F43" t="n">
-        <v>1.776936293222191</v>
+        <v>1.594729311471248</v>
       </c>
       <c r="G43" t="n">
-        <v>1.746511035450367</v>
+        <v>1.578680583191157</v>
       </c>
       <c r="H43" t="n">
-        <v>2.089821558104168</v>
+        <v>1.804355555487131</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>mv_f0_lv_THE_PARKWAY_KARKALLA</t>
+          <t>mv_f0_lv_LEOPOLD_WENDY</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mv_f0_lv_the_parkway_karkalla</t>
+          <t>mv_f0_lv_leopold_wendy</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>1.602857019811987</v>
+        <v>1.568190910897838</v>
       </c>
       <c r="F44" t="n">
-        <v>2.007535091835931</v>
+        <v>1.576109800822102</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.1539860313094596</v>
+        <v>1.568190910897838</v>
       </c>
       <c r="H44" t="n">
-        <v>3.451609343200403</v>
+        <v>1.725986256915686</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mv_f0_lv_P12_SCHOOL_ORMOND</t>
+          <t>mv_f0_lv_SALLYS_RUN_ORMOND</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mv_f0_lv_p12_school_ormond</t>
+          <t>mv_f0_lv_sallys_run_ormond</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.55251523165836</v>
+        <v>1.436712861351326</v>
       </c>
       <c r="F45" t="n">
-        <v>1.618429206733821</v>
+        <v>1.444117217388214</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.55251523165836</v>
+        <v>1.436712861351326</v>
       </c>
       <c r="H45" t="n">
-        <v>1.833522862058025</v>
+        <v>1.582763166331365</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LEOPOLD_WENDY</t>
+          <t>mv_f0_lv_P12_SCHOOL_ORMOND</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mv_f0_lv_leopold_wendy</t>
+          <t>mv_f0_lv_p12_school_ormond</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>1.039016301612508</v>
+        <v>1.297204486834543</v>
       </c>
       <c r="F46" t="n">
-        <v>1.179887796148207</v>
+        <v>1.40370113637698</v>
       </c>
       <c r="G46" t="n">
-        <v>0.6838335889237817</v>
+        <v>-1.297204486834543</v>
       </c>
       <c r="H46" t="n">
-        <v>1.725986256915686</v>
+        <v>1.833522862058025</v>
       </c>
     </row>
   </sheetData>
@@ -1825,7 +1825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT5"/>
+  <dimension ref="A1:AT3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2335,286 +2335,6 @@
         <v>4.511091451491119</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>4.815347547532919</v>
-      </c>
-      <c r="C4" t="n">
-        <v>6.788283186385279</v>
-      </c>
-      <c r="D4" t="n">
-        <v>7.831391298025039</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4.661558617027687</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4.073331013099363</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6.433188159639389</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.410491074845837</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-1.804011149045639</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.941212610047851</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.76897759749469</v>
-      </c>
-      <c r="L4" t="n">
-        <v>8.87081463679926</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.2308245494646</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5.597906160455899</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.753071081803782</v>
-      </c>
-      <c r="P4" t="n">
-        <v>6.854716468633505</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.314837735304167</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4.902895107817287</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5.868084797810926</v>
-      </c>
-      <c r="T4" t="n">
-        <v>7.157207309913659</v>
-      </c>
-      <c r="U4" t="n">
-        <v>5.68550482611553</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2.502469653502331</v>
-      </c>
-      <c r="W4" t="n">
-        <v>4.51187544930951</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.7103654253774536</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3.633040924699294</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>6.138550158360403</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.015349480280895</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>3.946742037646004</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.465467543363239</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>4.585434185988635</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>6.458134933603422</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>5.542020565709208</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>5.099156447661652</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.498235525777211</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.6554332035413</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.90312941062928</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.022796860994648</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.881475291000458</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>4.488739066789844</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>8.955805805452631</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>4.199619127266963</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>4.065511262670586</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>6.45957214738122</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>7.74850836887034</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.512585863858085</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.955719120830651</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4.419377936704183</v>
-      </c>
-      <c r="C5" t="n">
-        <v>6.035667252229203</v>
-      </c>
-      <c r="D5" t="n">
-        <v>8.122498456491556</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3.759987375384824</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.795939931843009</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6.750472035715728</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.992811271348437</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-1.811640803918714</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.264758073634495</v>
-      </c>
-      <c r="K5" t="n">
-        <v>6.318794409014831</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9.41812697629026</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5.629819819323682</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.85523515680093</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.446442894451039</v>
-      </c>
-      <c r="P5" t="n">
-        <v>6.290650218988013</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.567796235521712</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3.330268451273902</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6.154243510425427</v>
-      </c>
-      <c r="T5" t="n">
-        <v>5.18179595078616</v>
-      </c>
-      <c r="U5" t="n">
-        <v>5.411330738498368</v>
-      </c>
-      <c r="V5" t="n">
-        <v>2.565559915455205</v>
-      </c>
-      <c r="W5" t="n">
-        <v>4.209706816671641</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.3093179592769033</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3.726312405528901</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.252324639490006</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.388388224237893</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.684826466326964</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>10.91457897047595</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>6.06304648491475</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>7.91731378144539</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>5.649651605784747</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>5.570274127243895</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.399506451227843</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5.826279491014663</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.447638356151707</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.089821558104168</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.841111454101297</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>3.992824055543498</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>8.434953893871114</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>5.285746203960869</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.377205631930341</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3.75654201586195</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>6.736669144840821</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>5.513848033272076</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.984183574148563</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/nando/Nando_final/metrics/net_3_Urban_HPK11/trafo_loading_compare.xlsx
+++ b/nando/Nando_final/metrics/net_3_Urban_HPK11/trafo_loading_compare.xlsx
@@ -482,136 +482,136 @@
         <v>88</v>
       </c>
       <c r="E2" t="n">
-        <v>4.67376308155988</v>
+        <v>2.506357509899432</v>
       </c>
       <c r="F2" t="n">
-        <v>4.795306402110056</v>
+        <v>2.62063779094185</v>
       </c>
       <c r="G2" t="n">
-        <v>4.534942738925516</v>
+        <v>-1.840465816694231</v>
       </c>
       <c r="H2" t="n">
-        <v>11.06031860826563</v>
+        <v>8.688255942402883</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mv_f0_lv_CHATSWOOD_FLEET</t>
+          <t>mv_f0_lv_TUILERIES_PROVENCE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mv_f0_lv_chatswood_fleet</t>
+          <t>mv_f0_lv_tuileries_provence</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>10.33870494468933</v>
+        <v>7.601308378263614</v>
       </c>
       <c r="F3" t="n">
-        <v>10.35271820963854</v>
+        <v>7.678629048772241</v>
       </c>
       <c r="G3" t="n">
-        <v>10.33870494468933</v>
+        <v>-7.601308378263614</v>
       </c>
       <c r="H3" t="n">
-        <v>10.87717908040791</v>
+        <v>8.688255942402883</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HIGHMOUNT_ORMOND</t>
+          <t>mv_f0_lv_GOLDEN_CHERRYWOOD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mv_f0_lv_highmount_ormond</t>
+          <t>mv_f0_lv_golden_cherrywood</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>8.703654914963598</v>
+        <v>7.135092748670422</v>
       </c>
       <c r="F4" t="n">
-        <v>8.714150178849192</v>
+        <v>7.179677680150989</v>
       </c>
       <c r="G4" t="n">
-        <v>8.703654914963598</v>
+        <v>-7.135092748670422</v>
       </c>
       <c r="H4" t="n">
-        <v>9.131211298107832</v>
+        <v>7.933981388425085</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TANGERINE_NORWEGIAN</t>
+          <t>mv_f0_lv_CHATSWOOD_FLEET</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mv_f0_lv_tangerine_norwegian</t>
+          <t>mv_f0_lv_chatswood_fleet</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>8.662144647756186</v>
+        <v>6.818312589858143</v>
       </c>
       <c r="F5" t="n">
-        <v>8.709430644467428</v>
+        <v>6.954827977750348</v>
       </c>
       <c r="G5" t="n">
-        <v>8.662144647756186</v>
+        <v>-6.818312589858143</v>
       </c>
       <c r="H5" t="n">
-        <v>9.568473645492205</v>
+        <v>8.189533077993048</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TUILERIES_PROVENCE</t>
+          <t>mv_f0_lv_SPRINGFLD_KATHERINE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mv_f0_lv_tuileries_provence</t>
+          <t>mv_f0_lv_springfld_katherine</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>8.566107564361307</v>
+        <v>5.982677699384602</v>
       </c>
       <c r="F6" t="n">
-        <v>8.566469115959013</v>
+        <v>5.987533703124246</v>
       </c>
       <c r="G6" t="n">
-        <v>8.566107564361307</v>
+        <v>-5.982677699384602</v>
       </c>
       <c r="H6" t="n">
-        <v>8.644811506267644</v>
+        <v>6.223773927755985</v>
       </c>
     </row>
     <row r="7">
@@ -632,256 +632,256 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>7.641333227445244</v>
+        <v>5.771399767581851</v>
       </c>
       <c r="F7" t="n">
-        <v>7.729689662995275</v>
+        <v>5.798343374883084</v>
       </c>
       <c r="G7" t="n">
-        <v>7.641333227445244</v>
+        <v>-5.771399767581851</v>
       </c>
       <c r="H7" t="n">
-        <v>8.806721057035574</v>
+        <v>6.329728179725372</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mv_f0_lv_VON_NIDA_DULWICH</t>
+          <t>mv_f0_lv_THE_PARKWAY_KARKALLA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mv_f0_lv_von_nida_dulwich</t>
+          <t>mv_f0_lv_the_parkway_karkalla</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>7.578714805990799</v>
+        <v>5.240444094848334</v>
       </c>
       <c r="F8" t="n">
-        <v>7.737742686695906</v>
+        <v>5.531440355078873</v>
       </c>
       <c r="G8" t="n">
-        <v>7.578714805990799</v>
+        <v>-5.240444094848334</v>
       </c>
       <c r="H8" t="n">
-        <v>9.139401762100775</v>
+        <v>7.010918068270229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mv_f0_lv_EDEYS_PIONEER</t>
+          <t>mv_f0_lv_NORWEGIAN_GLASSCOCKS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mv_f0_lv_edeys_pioneer</t>
+          <t>mv_f0_lv_norwegian_glasscocks</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>7.560760690963598</v>
+        <v>4.30450184569853</v>
       </c>
       <c r="F9" t="n">
-        <v>8.331386909907119</v>
+        <v>4.376229807202228</v>
       </c>
       <c r="G9" t="n">
-        <v>7.560760690963598</v>
+        <v>-4.30450184569853</v>
       </c>
       <c r="H9" t="n">
-        <v>11.06031860826563</v>
+        <v>5.093584341907388</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mv_f0_lv_CORAL_CLAUD</t>
+          <t>mv_f0_lv_HIGHMOUNT_ORMOND</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mv_f0_lv_coral_claud</t>
+          <t>mv_f0_lv_highmount_ormond</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>6.742923501014221</v>
+        <v>4.250409452004465</v>
       </c>
       <c r="F10" t="n">
-        <v>6.743010711564586</v>
+        <v>4.253909916982875</v>
       </c>
       <c r="G10" t="n">
-        <v>6.742923501014221</v>
+        <v>-4.250409452004465</v>
       </c>
       <c r="H10" t="n">
-        <v>6.777218044965949</v>
+        <v>4.42294661355626</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GERALDINE_PAULINE</t>
+          <t>mv_f0_lv_CHISHOLM_KERSHAW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mv_f0_lv_geraldine_pauline</t>
+          <t>mv_f0_lv_chisholm_kershaw</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>6.42105124386983</v>
+        <v>4.236176259091916</v>
       </c>
       <c r="F11" t="n">
-        <v>6.52697163988903</v>
+        <v>4.291561673638149</v>
       </c>
       <c r="G11" t="n">
-        <v>6.42105124386983</v>
+        <v>-4.236176259091916</v>
       </c>
       <c r="H11" t="n">
-        <v>7.592144626787441</v>
+        <v>4.923426068510512</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TOOMAH_STRATHARD</t>
+          <t>mv_f0_lv_NIMBUS_AMBER</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mv_f0_lv_toomah_strathard</t>
+          <t>mv_f0_lv_nimbus_amber</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>6.170552281710302</v>
+        <v>3.963099514818241</v>
       </c>
       <c r="F12" t="n">
-        <v>6.170699426104486</v>
+        <v>3.964363297852441</v>
       </c>
       <c r="G12" t="n">
-        <v>6.170552281710302</v>
+        <v>-3.963099514818241</v>
       </c>
       <c r="H12" t="n">
-        <v>6.213166199695049</v>
+        <v>4.063192436680399</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LEOPOLD_HAZEL</t>
+          <t>mv_f0_lv_EDEYS_MOLLISONS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mv_f0_lv_leopold_hazel</t>
+          <t>mv_f0_lv_edeys_mollisons</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>6.098715924784443</v>
+        <v>3.943065480562028</v>
       </c>
       <c r="F13" t="n">
-        <v>6.106011542548398</v>
+        <v>4.202463157283113</v>
       </c>
       <c r="G13" t="n">
-        <v>6.098715924784443</v>
+        <v>-3.943065480562028</v>
       </c>
       <c r="H13" t="n">
-        <v>6.397113355260814</v>
+        <v>5.39665799716429</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mv_f0_lv_NORWEGIAN_GLASSCOCKS</t>
+          <t>mv_f0_lv_LESLEY_AMY</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mv_f0_lv_norwegian_glasscocks</t>
+          <t>mv_f0_lv_lesley_amy</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>6.016597126595563</v>
+        <v>3.631336194600705</v>
       </c>
       <c r="F14" t="n">
-        <v>6.028980183750392</v>
+        <v>4.053710284872703</v>
       </c>
       <c r="G14" t="n">
-        <v>6.016597126595563</v>
+        <v>3.631336194600705</v>
       </c>
       <c r="H14" t="n">
-        <v>6.402810891623311</v>
+        <v>5.432992242648057</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_TANGERINE</t>
+          <t>mv_f0_lv_KERSHAW_ORMOND</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_tangerine</t>
+          <t>mv_f0_lv_kershaw_ormond</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.987472229624299</v>
+        <v>3.272452473539163</v>
       </c>
       <c r="F15" t="n">
-        <v>6.055097491211796</v>
+        <v>3.298695551858969</v>
       </c>
       <c r="G15" t="n">
-        <v>5.987472229624299</v>
+        <v>-3.272452473539163</v>
       </c>
       <c r="H15" t="n">
-        <v>6.88990335029624</v>
+        <v>3.687720040634836</v>
       </c>
     </row>
     <row r="16">
@@ -902,196 +902,196 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>5.640198490131667</v>
+        <v>3.001688700353926</v>
       </c>
       <c r="F16" t="n">
-        <v>5.640297439787684</v>
+        <v>3.009199066840802</v>
       </c>
       <c r="G16" t="n">
-        <v>5.640198490131667</v>
+        <v>-3.001688700353926</v>
       </c>
       <c r="H16" t="n">
-        <v>5.673608087435007</v>
+        <v>3.214159804373079</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFIELD_JANET</t>
+          <t>mv_f0_lv_TOOMAH_STRATHARD</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfield_janet</t>
+          <t>mv_f0_lv_toomah_strathard</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>5.557826824733615</v>
+        <v>2.896852271682006</v>
       </c>
       <c r="F17" t="n">
-        <v>5.821565834043804</v>
+        <v>2.926419237561311</v>
       </c>
       <c r="G17" t="n">
-        <v>5.557826824733615</v>
+        <v>-2.896852271682006</v>
       </c>
       <c r="H17" t="n">
-        <v>7.290221048453379</v>
+        <v>3.311793797706731</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GREENVIEW_SNOWDONIA</t>
+          <t>mv_f0_lv_HALLAM_EDEYS</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mv_f0_lv_greenview_snowdonia</t>
+          <t>mv_f0_lv_hallam_edeys</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.334215010386488</v>
+        <v>2.892014108186359</v>
       </c>
       <c r="F18" t="n">
-        <v>5.391198958847043</v>
+        <v>2.914874318655032</v>
       </c>
       <c r="G18" t="n">
-        <v>5.334215010386488</v>
+        <v>-2.892014108186359</v>
       </c>
       <c r="H18" t="n">
-        <v>6.115992751717688</v>
+        <v>3.256358302054871</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GOLDEN_CHERRYWOOD</t>
+          <t>mv_f0_lv_VON_NIDA_DULWICH</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mv_f0_lv_golden_cherrywood</t>
+          <t>mv_f0_lv_von_nida_dulwich</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>5.297386540121654</v>
+        <v>2.82625488828223</v>
       </c>
       <c r="F19" t="n">
-        <v>5.302066238367832</v>
+        <v>3.128273790895261</v>
       </c>
       <c r="G19" t="n">
-        <v>5.297386540121654</v>
+        <v>1.341036993249256</v>
       </c>
       <c r="H19" t="n">
-        <v>5.520102144824037</v>
+        <v>4.167291881531487</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mv_f0_lv_NIMBUS_AMBER</t>
+          <t>mv_f0_lv_SHERWOOD_FLEET</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mv_f0_lv_nimbus_amber</t>
+          <t>mv_f0_lv_sherwood_fleet</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>5.142212488996437</v>
+        <v>2.727147560626675</v>
       </c>
       <c r="F20" t="n">
-        <v>5.217208207871479</v>
+        <v>2.728438289872758</v>
       </c>
       <c r="G20" t="n">
-        <v>5.142212488996437</v>
+        <v>-2.727147560626675</v>
       </c>
       <c r="H20" t="n">
-        <v>6.023638720901634</v>
+        <v>2.811062304335735</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mv_f0_lv_MALABAR_BYRON</t>
+          <t>mv_f0_lv_HALLAM_RD_RETIREMENT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mv_f0_lv_malabar_byron</t>
+          <t>mv_f0_lv_hallam_rd_retirement</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.05004964324441</v>
+        <v>2.518910314922997</v>
       </c>
       <c r="F21" t="n">
-        <v>5.108520282724255</v>
+        <v>2.538639460930062</v>
       </c>
       <c r="G21" t="n">
-        <v>5.05004964324441</v>
+        <v>2.518910314922997</v>
       </c>
       <c r="H21" t="n">
-        <v>5.820749377104562</v>
+        <v>2.834791840127945</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mv_f0_lv_RALEIGH_LOWDEN</t>
+          <t>mv_f0_lv_ORMOND_TANGERINE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mv_f0_lv_raleigh_lowden</t>
+          <t>mv_f0_lv_ormond_tangerine</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>5.032876280621943</v>
+        <v>2.457581536821828</v>
       </c>
       <c r="F22" t="n">
-        <v>5.049865737252153</v>
+        <v>2.58010549454719</v>
       </c>
       <c r="G22" t="n">
-        <v>5.032876280621943</v>
+        <v>-2.457581536821828</v>
       </c>
       <c r="H22" t="n">
-        <v>5.446760694711514</v>
+        <v>3.243226082952622</v>
       </c>
     </row>
     <row r="23">
@@ -1112,706 +1112,706 @@
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>4.777956465714333</v>
+        <v>1.945170435141205</v>
       </c>
       <c r="F23" t="n">
-        <v>5.047832570725505</v>
+        <v>2.293262935566214</v>
       </c>
       <c r="G23" t="n">
-        <v>4.777956465714333</v>
+        <v>-1.945170435141205</v>
       </c>
       <c r="H23" t="n">
-        <v>6.406374616502347</v>
+        <v>3.159817243845014</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LESLEY_CARMEN</t>
+          <t>mv_f0_lv_GERALDINE_PAULINE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mv_f0_lv_lesley_carmen</t>
+          <t>mv_f0_lv_geraldine_pauline</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.345684515766015</v>
+        <v>1.837754344974178</v>
       </c>
       <c r="F24" t="n">
-        <v>4.345751129176762</v>
+        <v>2.22441779299859</v>
       </c>
       <c r="G24" t="n">
-        <v>4.345684515766015</v>
+        <v>-1.837754344974178</v>
       </c>
       <c r="H24" t="n">
-        <v>4.369746231677226</v>
+        <v>3.09102745381249</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HALLAM_EDEYS</t>
+          <t>mv_f0_lv_CORAL_CLAUD</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hallam_edeys</t>
+          <t>mv_f0_lv_coral_claud</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>4.300457061557832</v>
+        <v>1.636432673079453</v>
       </c>
       <c r="F25" t="n">
-        <v>4.316161911813845</v>
+        <v>1.641876271353205</v>
       </c>
       <c r="G25" t="n">
-        <v>4.300457061557832</v>
+        <v>-1.636432673079453</v>
       </c>
       <c r="H25" t="n">
-        <v>4.668319414469792</v>
+        <v>1.770020834646044</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFLD_KATHERINE</t>
+          <t>mv_f0_lv_EDEYS_PIONEER</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfld_katherine</t>
+          <t>mv_f0_lv_edeys_pioneer</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>4.279093313526406</v>
+        <v>1.621260520090678</v>
       </c>
       <c r="F26" t="n">
-        <v>4.361576902013026</v>
+        <v>1.624371067159061</v>
       </c>
       <c r="G26" t="n">
-        <v>4.279093313526406</v>
+        <v>-1.621260520090678</v>
       </c>
       <c r="H26" t="n">
-        <v>5.123316913236309</v>
+        <v>1.721737830060498</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_STRATHAIRD</t>
+          <t>mv_f0_lv_COMMUNITY_HARRINGTON</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_strathaird</t>
+          <t>mv_f0_lv_community_harrington</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.028795177174223</v>
+        <v>1.597541056692343</v>
       </c>
       <c r="F27" t="n">
-        <v>4.197903758501883</v>
+        <v>1.610845661490978</v>
       </c>
       <c r="G27" t="n">
-        <v>4.028795177174223</v>
+        <v>-1.597541056692343</v>
       </c>
       <c r="H27" t="n">
-        <v>5.208288876191713</v>
+        <v>1.80414772968869</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mv_f0_lv_OAKGROVE_OXENFORD</t>
+          <t>mv_f0_lv_TIMMS_STRATHAIRD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mv_f0_lv_oakgrove_oxenford</t>
+          <t>mv_f0_lv_timms_strathaird</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>3.952848069203633</v>
+        <v>1.547123563329004</v>
       </c>
       <c r="F28" t="n">
-        <v>3.968152842430217</v>
+        <v>1.967121854490061</v>
       </c>
       <c r="G28" t="n">
-        <v>3.952848069203633</v>
+        <v>-1.547123563329004</v>
       </c>
       <c r="H28" t="n">
-        <v>4.301027796758426</v>
+        <v>2.762021530322357</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mv_f0_lv_MICHELLE_SIMON</t>
+          <t>mv_f0_lv_P12_SCHOOL_ORMOND</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mv_f0_lv_michelle_simon</t>
+          <t>mv_f0_lv_p12_school_ormond</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>3.898179694329004</v>
+        <v>1.505506141546534</v>
       </c>
       <c r="F29" t="n">
-        <v>3.96283720312712</v>
+        <v>1.505523064093401</v>
       </c>
       <c r="G29" t="n">
-        <v>3.898179694329004</v>
+        <v>1.505506141546534</v>
       </c>
       <c r="H29" t="n">
-        <v>4.611112909440639</v>
+        <v>1.512644368416636</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mv_f0_lv_KERSHAW_ORMOND</t>
+          <t>mv_f0_lv_GREENVIEW_SNOWDONIA</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mv_f0_lv_kershaw_ormond</t>
+          <t>mv_f0_lv_greenview_snowdonia</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.804851347164465</v>
+        <v>1.252650202468573</v>
       </c>
       <c r="F30" t="n">
-        <v>4.684273111958299</v>
+        <v>1.26937241859346</v>
       </c>
       <c r="G30" t="n">
-        <v>3.804851347164465</v>
+        <v>-1.252650202468573</v>
       </c>
       <c r="H30" t="n">
-        <v>6.53716187369622</v>
+        <v>1.45801282648096</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TIMMS_STRATHAIRD</t>
+          <t>mv_f0_lv_LEOPOLD_HAZEL</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mv_f0_lv_timms_strathaird</t>
+          <t>mv_f0_lv_leopold_hazel</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>3.530775127110449</v>
+        <v>1.150975600984633</v>
       </c>
       <c r="F31" t="n">
-        <v>3.878995877736294</v>
+        <v>1.27225390209218</v>
       </c>
       <c r="G31" t="n">
-        <v>3.530775127110449</v>
+        <v>-0.5421117572298542</v>
       </c>
       <c r="H31" t="n">
-        <v>5.137086436064401</v>
+        <v>1.693087358214488</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HADLEY_CHESTERFIELD</t>
+          <t>mv_f0_lv_MICHELLE_SIMON</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hadley_chesterfield</t>
+          <t>mv_f0_lv_michelle_simon</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>3.517246481454302</v>
+        <v>1.077431736028387</v>
       </c>
       <c r="F32" t="n">
-        <v>3.654962467080907</v>
+        <v>1.507796657786879</v>
       </c>
       <c r="G32" t="n">
-        <v>3.517246481454302</v>
+        <v>-1.054794584472322</v>
       </c>
       <c r="H32" t="n">
-        <v>4.511091451491119</v>
+        <v>2.13222632050071</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mv_f0_lv_EDEYS_MOLLISONS</t>
+          <t>mv_f0_lv_RALEIGH_LOWDEN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mv_f0_lv_edeys_mollisons</t>
+          <t>mv_f0_lv_raleigh_lowden</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.291751593635354</v>
+        <v>1.060903954401588</v>
       </c>
       <c r="F33" t="n">
-        <v>3.300771747233533</v>
+        <v>1.140070643574751</v>
       </c>
       <c r="G33" t="n">
-        <v>3.291751593635354</v>
+        <v>-1.060903954401588</v>
       </c>
       <c r="H33" t="n">
-        <v>3.53560723358288</v>
+        <v>1.478329243376779</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SHERWOOD_FLEET</t>
+          <t>mv_f0_lv_LEOPOLD_WENDY</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mv_f0_lv_sherwood_fleet</t>
+          <t>mv_f0_lv_leopold_wendy</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>3.268164578145162</v>
+        <v>1.033628907757514</v>
       </c>
       <c r="F34" t="n">
-        <v>3.31907653751956</v>
+        <v>1.046010626100067</v>
       </c>
       <c r="G34" t="n">
-        <v>3.268164578145162</v>
+        <v>-0.1604665415663469</v>
       </c>
       <c r="H34" t="n">
-        <v>3.847275406976813</v>
+        <v>1.194095449323861</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LESLEY_AMY</t>
+          <t>mv_f0_lv_SALLYS_RUN_ORMOND</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mv_f0_lv_lesley_amy</t>
+          <t>mv_f0_lv_sallys_run_ormond</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>3.248770189155404</v>
+        <v>0.980914217063602</v>
       </c>
       <c r="F35" t="n">
-        <v>3.322072485391456</v>
+        <v>1.064943145877004</v>
       </c>
       <c r="G35" t="n">
-        <v>3.248770189155404</v>
+        <v>0.980914217063602</v>
       </c>
       <c r="H35" t="n">
-        <v>3.942785935554667</v>
+        <v>1.395535975673676</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mv_f0_lv_COMMUNITY_HARRINGTON</t>
+          <t>mv_f0_lv_OAKGROVE_OXENFORD</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mv_f0_lv_community_harrington</t>
+          <t>mv_f0_lv_oakgrove_oxenford</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.171313186205175</v>
+        <v>0.9759697003584664</v>
       </c>
       <c r="F36" t="n">
-        <v>3.183808790805393</v>
+        <v>1.000947634826168</v>
       </c>
       <c r="G36" t="n">
-        <v>3.171313186205175</v>
+        <v>0.9759697003584664</v>
       </c>
       <c r="H36" t="n">
-        <v>3.453112922562173</v>
+        <v>1.198184262541744</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mv_f0_lv_CHISHOLM_KERSHAW</t>
+          <t>mv_f0_lv_TANGERINE_NORWEGIAN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mv_f0_lv_chisholm_kershaw</t>
+          <t>mv_f0_lv_tangerine_norwegian</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>2.788889228499116</v>
+        <v>0.9129788600518012</v>
       </c>
       <c r="F37" t="n">
-        <v>2.799097877410158</v>
+        <v>0.9690682018862853</v>
       </c>
       <c r="G37" t="n">
-        <v>2.788889228499116</v>
+        <v>-0.3249042643697244</v>
       </c>
       <c r="H37" t="n">
-        <v>3.027731851336114</v>
+        <v>1.237883124421526</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HALLAM_RD_RETIREMENT</t>
+          <t>mv_f0_lv_LESLEY_CARMEN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hallam_rd_retirement</t>
+          <t>mv_f0_lv_lesley_carmen</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>2.365045981897813</v>
+        <v>0.8402401250605598</v>
       </c>
       <c r="F38" t="n">
-        <v>2.461922019803509</v>
+        <v>0.8931587899023001</v>
       </c>
       <c r="G38" t="n">
-        <v>2.365045981897813</v>
+        <v>-0.8402401250605598</v>
       </c>
       <c r="H38" t="n">
-        <v>3.048871643234385</v>
+        <v>1.14310834098616</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mv_f0_lv_VIEWSIDE_NEESAN</t>
+          <t>mv_f0_lv_MALABAR_BYRON</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mv_f0_lv_viewside_neesan</t>
+          <t>mv_f0_lv_malabar_byron</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.043148938032417</v>
+        <v>0.7806554691151302</v>
       </c>
       <c r="F39" t="n">
-        <v>2.104416910594919</v>
+        <v>1.050619170369556</v>
       </c>
       <c r="G39" t="n">
-        <v>2.043148938032417</v>
+        <v>0.7031199610938739</v>
       </c>
       <c r="H39" t="n">
-        <v>2.547245110022317</v>
+        <v>1.483775430209004</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mv_f0_lv_BARINGA_PARK_CASPIAN</t>
+          <t>mv_f0_lv_HADLEY_CHESTERFIELD</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mv_f0_lv_baringa_park_caspian</t>
+          <t>mv_f0_lv_hadley_chesterfield</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>1.933007051943891</v>
+        <v>0.6527336436366271</v>
       </c>
       <c r="F40" t="n">
-        <v>2.402135026462097</v>
+        <v>0.9173446317393896</v>
       </c>
       <c r="G40" t="n">
-        <v>1.933007051943891</v>
+        <v>-0.6445618386515983</v>
       </c>
       <c r="H40" t="n">
-        <v>3.3590983612545</v>
+        <v>1.297295482288225</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFIELD_HUNTNGTN</t>
+          <t>mv_f0_lv_ORMOND_STRATHAIRD</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfield_huntngtn</t>
+          <t>mv_f0_lv_ormond_strathaird</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>1.918467312718482</v>
+        <v>0.646458534197043</v>
       </c>
       <c r="F41" t="n">
-        <v>1.918942891756052</v>
+        <v>0.8291307877342984</v>
       </c>
       <c r="G41" t="n">
-        <v>1.918467312718482</v>
+        <v>0.5191813042981313</v>
       </c>
       <c r="H41" t="n">
-        <v>1.961187236077567</v>
+        <v>1.165639838495174</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>mv_f0_lv_THE_PARKWAY_KARKALLA</t>
+          <t>mv_f0_lv_BARINGA_PARK_CASPIAN</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mv_f0_lv_the_parkway_karkalla</t>
+          <t>mv_f0_lv_baringa_park_caspian</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.756843051121447</v>
+        <v>0.6178875274035853</v>
       </c>
       <c r="F42" t="n">
-        <v>2.441051062767997</v>
+        <v>0.6179649474139653</v>
       </c>
       <c r="G42" t="n">
-        <v>-1.756843051121447</v>
+        <v>0.009781600657788658</v>
       </c>
       <c r="H42" t="n">
-        <v>3.451609343200403</v>
+        <v>0.627669128061374</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_SCHOOL</t>
+          <t>mv_f0_lv_SPRINGFIELD_JANET</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_school</t>
+          <t>mv_f0_lv_springfield_janet</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>1.578680583191157</v>
+        <v>0.4463374927275385</v>
       </c>
       <c r="F43" t="n">
-        <v>1.594729311471248</v>
+        <v>0.6118886757734596</v>
       </c>
       <c r="G43" t="n">
-        <v>1.578680583191157</v>
+        <v>-0.41855775482661</v>
       </c>
       <c r="H43" t="n">
-        <v>1.804355555487131</v>
+        <v>0.8648952475541485</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LEOPOLD_WENDY</t>
+          <t>mv_f0_lv_ORMOND_SCHOOL</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mv_f0_lv_leopold_wendy</t>
+          <t>mv_f0_lv_ormond_school</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>1.568190910897838</v>
+        <v>0.2504477928385813</v>
       </c>
       <c r="F44" t="n">
-        <v>1.576109800822102</v>
+        <v>0.3210478139697901</v>
       </c>
       <c r="G44" t="n">
-        <v>1.568190910897838</v>
+        <v>0.2504477928385813</v>
       </c>
       <c r="H44" t="n">
-        <v>1.725986256915686</v>
+        <v>0.4513149178667053</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SALLYS_RUN_ORMOND</t>
+          <t>mv_f0_lv_VIEWSIDE_NEESAN</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mv_f0_lv_sallys_run_ormond</t>
+          <t>mv_f0_lv_viewside_neesan</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.436712861351326</v>
+        <v>0.2283263850320827</v>
       </c>
       <c r="F45" t="n">
-        <v>1.444117217388214</v>
+        <v>0.3140703230616121</v>
       </c>
       <c r="G45" t="n">
-        <v>1.436712861351326</v>
+        <v>-0.2283263850320827</v>
       </c>
       <c r="H45" t="n">
-        <v>1.582763166331365</v>
+        <v>0.4439817344352601</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>mv_f0_lv_P12_SCHOOL_ORMOND</t>
+          <t>mv_f0_lv_SPRINGFIELD_HUNTNGTN</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mv_f0_lv_p12_school_ormond</t>
+          <t>mv_f0_lv_springfield_huntngtn</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>1.297204486834543</v>
+        <v>0.209675671797898</v>
       </c>
       <c r="F46" t="n">
-        <v>1.40370113637698</v>
+        <v>0.2176202948360347</v>
       </c>
       <c r="G46" t="n">
-        <v>-1.297204486834543</v>
+        <v>-0.209675671797898</v>
       </c>
       <c r="H46" t="n">
-        <v>1.833522862058025</v>
+        <v>0.2679397720709034</v>
       </c>
     </row>
   </sheetData>
@@ -2060,139 +2060,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.284135886575395</v>
+        <v>-1.517864426795253</v>
       </c>
       <c r="C2" t="n">
-        <v>3.604668341648839</v>
+        <v>1.198184262541744</v>
       </c>
       <c r="D2" t="n">
-        <v>10.87717908040791</v>
+        <v>-8.189533077993048</v>
       </c>
       <c r="E2" t="n">
-        <v>6.115992751717688</v>
+        <v>-1.45801282648096</v>
       </c>
       <c r="F2" t="n">
-        <v>1.07254082063271</v>
+        <v>-3.687720040634836</v>
       </c>
       <c r="G2" t="n">
-        <v>4.279349909384258</v>
+        <v>1.483775430209004</v>
       </c>
       <c r="H2" t="n">
-        <v>3.027731851336114</v>
+        <v>-3.548926449673321</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.760886111611061</v>
+        <v>1.512644368416636</v>
       </c>
       <c r="J2" t="n">
-        <v>1.804355555487131</v>
+        <v>0.4513149178667053</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5069157426332822</v>
+        <v>0.627669128061374</v>
       </c>
       <c r="L2" t="n">
-        <v>8.48740362245497</v>
+        <v>-6.514360814124345</v>
       </c>
       <c r="M2" t="n">
-        <v>3.932594708645873</v>
+        <v>-2.527669914317848</v>
       </c>
       <c r="N2" t="n">
-        <v>2.849301478156733</v>
+        <v>-0.1272772298989118</v>
       </c>
       <c r="O2" t="n">
-        <v>2.689053749313512</v>
+        <v>-2.811062304335735</v>
       </c>
       <c r="P2" t="n">
-        <v>5.520102144824037</v>
+        <v>-6.336204108915759</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.06031860826563</v>
+        <v>-1.520783210120857</v>
       </c>
       <c r="R2" t="n">
-        <v>3.453112922562173</v>
+        <v>-1.80414772968869</v>
       </c>
       <c r="S2" t="n">
-        <v>3.434869713816504</v>
+        <v>-5.74158147101322</v>
       </c>
       <c r="T2" t="n">
-        <v>8.806721057035574</v>
+        <v>-5.213071355438331</v>
       </c>
       <c r="U2" t="n">
-        <v>3.825432601013851</v>
+        <v>-0.8648952475541485</v>
       </c>
       <c r="V2" t="n">
-        <v>1.875747389359397</v>
+        <v>-0.1514115715248927</v>
       </c>
       <c r="W2" t="n">
-        <v>5.446760694711514</v>
+        <v>-0.6434786654263966</v>
       </c>
       <c r="X2" t="n">
-        <v>1.725986256915686</v>
+        <v>0.8731623661911669</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.630383361567816</v>
+        <v>-3.515419349489672</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.139401762100775</v>
+        <v>4.167291881531487</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.048871643234385</v>
+        <v>2.834791840127945</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.924463818156497</v>
+        <v>-0.3322255963356504</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.708628957062494</v>
+        <v>-1.502844511512862</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.185246479217369</v>
+        <v>0.02263715155606505</v>
       </c>
       <c r="AE2" t="n">
-        <v>6.397113355260814</v>
+        <v>0.6088638437547793</v>
       </c>
       <c r="AF2" t="n">
-        <v>4.26078625709124</v>
+        <v>-3.863006592956083</v>
       </c>
       <c r="AG2" t="n">
-        <v>5.249957860952218</v>
+        <v>-3.09102745381249</v>
       </c>
       <c r="AH2" t="n">
-        <v>-3.451609343200403</v>
+        <v>-3.469970121426439</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.321622799854804</v>
+        <v>-1.14310834098616</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.539052766042516</v>
+        <v>-0.4439817344352601</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.290662556371288</v>
+        <v>1.395535975673676</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.55475444275614</v>
+        <v>5.432992242648057</v>
       </c>
       <c r="AM2" t="n">
-        <v>6.213166199695049</v>
+        <v>-2.481910745657281</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.673608087435007</v>
+        <v>-3.214159804373079</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.53560723358288</v>
+        <v>-5.39665799716429</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.085041108952357</v>
+        <v>-3.243226082952622</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.131211298107832</v>
+        <v>-4.42294661355626</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.149538314926318</v>
+        <v>-0.730523626437396</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.755815650020168</v>
+        <v>0.5880745956820768</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.523401511417486</v>
+        <v>0.008171804985028785</v>
       </c>
     </row>
     <row r="3">
@@ -2200,139 +2200,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4.785749591275639</v>
+        <v>-2.16306720659321</v>
       </c>
       <c r="C3" t="n">
-        <v>4.301027796758426</v>
+        <v>0.7537551381751886</v>
       </c>
       <c r="D3" t="n">
-        <v>9.800230808970753</v>
+        <v>-5.447092101723239</v>
       </c>
       <c r="E3" t="n">
-        <v>4.552437269055289</v>
+        <v>-1.047287578456185</v>
       </c>
       <c r="F3" t="n">
-        <v>6.53716187369622</v>
+        <v>-2.857184906443489</v>
       </c>
       <c r="G3" t="n">
-        <v>5.820749377104562</v>
+        <v>-0.07753550802125631</v>
       </c>
       <c r="H3" t="n">
-        <v>2.550046605662118</v>
+        <v>-4.923426068510512</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.833522862058025</v>
+        <v>1.498367914676432</v>
       </c>
       <c r="J3" t="n">
-        <v>1.353005610895183</v>
+        <v>0.04958066781045734</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3590983612545</v>
+        <v>-0.6081059267457967</v>
       </c>
       <c r="L3" t="n">
-        <v>8.644811506267644</v>
+        <v>-8.688255942402883</v>
       </c>
       <c r="M3" t="n">
-        <v>4.668319414469792</v>
+        <v>-3.256358302054871</v>
       </c>
       <c r="N3" t="n">
-        <v>5.208288876191713</v>
+        <v>1.165639838495174</v>
       </c>
       <c r="O3" t="n">
-        <v>3.847275406976813</v>
+        <v>-2.643232816917616</v>
       </c>
       <c r="P3" t="n">
-        <v>5.07467093541927</v>
+        <v>-7.933981388425085</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.061202773661563</v>
+        <v>-1.721737830060498</v>
       </c>
       <c r="R3" t="n">
-        <v>2.889513449848177</v>
+        <v>-1.390934383695996</v>
       </c>
       <c r="S3" t="n">
-        <v>5.123316913236309</v>
+        <v>-6.223773927755985</v>
       </c>
       <c r="T3" t="n">
-        <v>6.475945397854915</v>
+        <v>-6.329728179725372</v>
       </c>
       <c r="U3" t="n">
-        <v>7.290221048453379</v>
+        <v>0.02777973790092858</v>
       </c>
       <c r="V3" t="n">
-        <v>1.961187236077567</v>
+        <v>-0.2679397720709034</v>
       </c>
       <c r="W3" t="n">
-        <v>4.618991866532372</v>
+        <v>-1.478329243376779</v>
       </c>
       <c r="X3" t="n">
-        <v>1.410395564879991</v>
+        <v>-1.194095449323861</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.402810891623311</v>
+        <v>-5.093584341907388</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.018027849880824</v>
+        <v>-1.485217895032974</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.681220320561241</v>
+        <v>2.203028789718049</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.137086436064401</v>
+        <v>-2.762021530322357</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.777218044965949</v>
+        <v>-1.770020834646044</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.611112909440639</v>
+        <v>-2.13222632050071</v>
       </c>
       <c r="AE3" t="n">
-        <v>5.800318494308073</v>
+        <v>-1.693087358214488</v>
       </c>
       <c r="AF3" t="n">
-        <v>6.023638720901634</v>
+        <v>-4.063192436680399</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.592144626787441</v>
+        <v>-0.5844812361358667</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.06207675904249044</v>
+        <v>-7.010918068270229</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.369746231677226</v>
+        <v>-0.5373719091349596</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.547245110022317</v>
+        <v>-0.01267103562890526</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.582763166331365</v>
+        <v>0.5662924584535283</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.942785935554667</v>
+        <v>1.829680146553354</v>
       </c>
       <c r="AM3" t="n">
-        <v>6.127938363725555</v>
+        <v>-3.311793797706731</v>
       </c>
       <c r="AN3" t="n">
-        <v>5.606788892828327</v>
+        <v>-2.789217596334773</v>
       </c>
       <c r="AO3" t="n">
-        <v>3.047895953687828</v>
+        <v>-2.489472963959766</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.88990335029624</v>
+        <v>-1.671936990691034</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.276098531819365</v>
+        <v>-4.077872290452671</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.406374616502347</v>
+        <v>-3.159817243845014</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.568473645492205</v>
+        <v>-1.237883124421526</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.511091451491119</v>
+        <v>-1.297295482288225</v>
       </c>
     </row>
   </sheetData>

--- a/nando/Nando_final/metrics/net_3_Urban_HPK11/trafo_loading_compare.xlsx
+++ b/nando/Nando_final/metrics/net_3_Urban_HPK11/trafo_loading_compare.xlsx
@@ -482,136 +482,136 @@
         <v>88</v>
       </c>
       <c r="E2" t="n">
-        <v>2.506357509899432</v>
+        <v>4.673763081568418</v>
       </c>
       <c r="F2" t="n">
-        <v>2.62063779094185</v>
+        <v>4.795306402115677</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.840465816694231</v>
+        <v>4.534942738939646</v>
       </c>
       <c r="H2" t="n">
-        <v>8.688255942402883</v>
+        <v>11.0603186085347</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TUILERIES_PROVENCE</t>
+          <t>mv_f0_lv_CHATSWOOD_FLEET</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mv_f0_lv_tuileries_provence</t>
+          <t>mv_f0_lv_chatswood_fleet</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>7.601308378263614</v>
+        <v>10.33870494477754</v>
       </c>
       <c r="F3" t="n">
-        <v>7.678629048772241</v>
+        <v>10.35271820972051</v>
       </c>
       <c r="G3" t="n">
-        <v>-7.601308378263614</v>
+        <v>10.33870494477754</v>
       </c>
       <c r="H3" t="n">
-        <v>8.688255942402883</v>
+        <v>10.87717908037843</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GOLDEN_CHERRYWOOD</t>
+          <t>mv_f0_lv_HIGHMOUNT_ORMOND</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mv_f0_lv_golden_cherrywood</t>
+          <t>mv_f0_lv_highmount_ormond</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>7.135092748670422</v>
+        <v>8.703654915021181</v>
       </c>
       <c r="F4" t="n">
-        <v>7.179677680150989</v>
+        <v>8.714150178900088</v>
       </c>
       <c r="G4" t="n">
-        <v>-7.135092748670422</v>
+        <v>8.703654915021181</v>
       </c>
       <c r="H4" t="n">
-        <v>7.933981388425085</v>
+        <v>9.131211298030582</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mv_f0_lv_CHATSWOOD_FLEET</t>
+          <t>mv_f0_lv_TANGERINE_NORWEGIAN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mv_f0_lv_chatswood_fleet</t>
+          <t>mv_f0_lv_tangerine_norwegian</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>6.818312589858143</v>
+        <v>8.662144647862014</v>
       </c>
       <c r="F5" t="n">
-        <v>6.954827977750348</v>
+        <v>8.709430644575297</v>
       </c>
       <c r="G5" t="n">
-        <v>-6.818312589858143</v>
+        <v>8.662144647862014</v>
       </c>
       <c r="H5" t="n">
-        <v>8.189533077993048</v>
+        <v>9.568473645623165</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFLD_KATHERINE</t>
+          <t>mv_f0_lv_TUILERIES_PROVENCE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfld_katherine</t>
+          <t>mv_f0_lv_tuileries_provence</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>5.982677699384602</v>
+        <v>8.566107564408835</v>
       </c>
       <c r="F6" t="n">
-        <v>5.987533703124246</v>
+        <v>8.566469116005242</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.982677699384602</v>
+        <v>8.566107564408835</v>
       </c>
       <c r="H6" t="n">
-        <v>6.223773927755985</v>
+        <v>8.644811506173951</v>
       </c>
     </row>
     <row r="7">
@@ -632,256 +632,256 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>5.771399767581851</v>
+        <v>7.641333227462532</v>
       </c>
       <c r="F7" t="n">
-        <v>5.798343374883084</v>
+        <v>7.729689663022477</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.771399767581851</v>
+        <v>7.641333227462532</v>
       </c>
       <c r="H7" t="n">
-        <v>6.329728179725372</v>
+        <v>8.806721057119923</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mv_f0_lv_THE_PARKWAY_KARKALLA</t>
+          <t>mv_f0_lv_VON_NIDA_DULWICH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mv_f0_lv_the_parkway_karkalla</t>
+          <t>mv_f0_lv_von_nida_dulwich</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>5.240444094848334</v>
+        <v>7.578714805994732</v>
       </c>
       <c r="F8" t="n">
-        <v>5.531440355078873</v>
+        <v>7.737742686684096</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.240444094848334</v>
+        <v>7.578714805994732</v>
       </c>
       <c r="H8" t="n">
-        <v>7.010918068270229</v>
+        <v>9.139401762027056</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mv_f0_lv_NORWEGIAN_GLASSCOCKS</t>
+          <t>mv_f0_lv_EDEYS_PIONEER</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mv_f0_lv_norwegian_glasscocks</t>
+          <t>mv_f0_lv_edeys_pioneer</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>4.30450184569853</v>
+        <v>7.560760691116123</v>
       </c>
       <c r="F9" t="n">
-        <v>4.376229807202228</v>
+        <v>8.331386910094489</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.30450184569853</v>
+        <v>7.560760691116123</v>
       </c>
       <c r="H9" t="n">
-        <v>5.093584341907388</v>
+        <v>11.0603186085347</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HIGHMOUNT_ORMOND</t>
+          <t>mv_f0_lv_CORAL_CLAUD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mv_f0_lv_highmount_ormond</t>
+          <t>mv_f0_lv_coral_claud</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>4.250409452004465</v>
+        <v>6.742923500949704</v>
       </c>
       <c r="F10" t="n">
-        <v>4.253909916982875</v>
+        <v>6.743010711500339</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.250409452004465</v>
+        <v>6.742923500949704</v>
       </c>
       <c r="H10" t="n">
-        <v>4.42294661355626</v>
+        <v>6.777218044954516</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mv_f0_lv_CHISHOLM_KERSHAW</t>
+          <t>mv_f0_lv_GERALDINE_PAULINE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mv_f0_lv_chisholm_kershaw</t>
+          <t>mv_f0_lv_geraldine_pauline</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>4.236176259091916</v>
+        <v>6.421051243729933</v>
       </c>
       <c r="F11" t="n">
-        <v>4.291561673638149</v>
+        <v>6.526971639747122</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.236176259091916</v>
+        <v>6.421051243729933</v>
       </c>
       <c r="H11" t="n">
-        <v>4.923426068510512</v>
+        <v>7.592144626623679</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mv_f0_lv_NIMBUS_AMBER</t>
+          <t>mv_f0_lv_TOOMAH_STRATHARD</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mv_f0_lv_nimbus_amber</t>
+          <t>mv_f0_lv_toomah_strathard</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>3.963099514818241</v>
+        <v>6.170552281707989</v>
       </c>
       <c r="F12" t="n">
-        <v>3.964363297852441</v>
+        <v>6.170699426101926</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.963099514818241</v>
+        <v>6.170552281707989</v>
       </c>
       <c r="H12" t="n">
-        <v>4.063192436680399</v>
+        <v>6.213166199657014</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mv_f0_lv_EDEYS_MOLLISONS</t>
+          <t>mv_f0_lv_LEOPOLD_HAZEL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mv_f0_lv_edeys_mollisons</t>
+          <t>mv_f0_lv_leopold_hazel</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>3.943065480562028</v>
+        <v>6.098715924806548</v>
       </c>
       <c r="F13" t="n">
-        <v>4.202463157283113</v>
+        <v>6.106011542566806</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.943065480562028</v>
+        <v>6.098715924806548</v>
       </c>
       <c r="H13" t="n">
-        <v>5.39665799716429</v>
+        <v>6.397113355207807</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LESLEY_AMY</t>
+          <t>mv_f0_lv_NORWEGIAN_GLASSCOCKS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mv_f0_lv_lesley_amy</t>
+          <t>mv_f0_lv_norwegian_glasscocks</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>3.631336194600705</v>
+        <v>6.016597126446982</v>
       </c>
       <c r="F14" t="n">
-        <v>4.053710284872703</v>
+        <v>6.02898018361211</v>
       </c>
       <c r="G14" t="n">
-        <v>3.631336194600705</v>
+        <v>6.016597126446982</v>
       </c>
       <c r="H14" t="n">
-        <v>5.432992242648057</v>
+        <v>6.402810891630764</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mv_f0_lv_KERSHAW_ORMOND</t>
+          <t>mv_f0_lv_ORMOND_TANGERINE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mv_f0_lv_kershaw_ormond</t>
+          <t>mv_f0_lv_ormond_tangerine</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.272452473539163</v>
+        <v>5.987472229701224</v>
       </c>
       <c r="F15" t="n">
-        <v>3.298695551858969</v>
+        <v>6.055097491291253</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.272452473539163</v>
+        <v>5.987472229701224</v>
       </c>
       <c r="H15" t="n">
-        <v>3.687720040634836</v>
+        <v>6.889903350395919</v>
       </c>
     </row>
     <row r="16">
@@ -902,196 +902,196 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>3.001688700353926</v>
+        <v>5.640198490143042</v>
       </c>
       <c r="F16" t="n">
-        <v>3.009199066840802</v>
+        <v>5.640297439798351</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.001688700353926</v>
+        <v>5.640198490143042</v>
       </c>
       <c r="H16" t="n">
-        <v>3.214159804373079</v>
+        <v>5.673608087326713</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TOOMAH_STRATHARD</t>
+          <t>mv_f0_lv_SPRINGFIELD_JANET</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mv_f0_lv_toomah_strathard</t>
+          <t>mv_f0_lv_springfield_janet</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>2.896852271682006</v>
+        <v>5.557826824656761</v>
       </c>
       <c r="F17" t="n">
-        <v>2.926419237561311</v>
+        <v>5.82156583395822</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.896852271682006</v>
+        <v>5.557826824656761</v>
       </c>
       <c r="H17" t="n">
-        <v>3.311793797706731</v>
+        <v>7.290221048335489</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HALLAM_EDEYS</t>
+          <t>mv_f0_lv_GREENVIEW_SNOWDONIA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hallam_edeys</t>
+          <t>mv_f0_lv_greenview_snowdonia</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.892014108186359</v>
+        <v>5.334215010425734</v>
       </c>
       <c r="F18" t="n">
-        <v>2.914874318655032</v>
+        <v>5.391198958886306</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.892014108186359</v>
+        <v>5.334215010425734</v>
       </c>
       <c r="H18" t="n">
-        <v>3.256358302054871</v>
+        <v>6.115992751759915</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mv_f0_lv_VON_NIDA_DULWICH</t>
+          <t>mv_f0_lv_GOLDEN_CHERRYWOOD</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mv_f0_lv_von_nida_dulwich</t>
+          <t>mv_f0_lv_golden_cherrywood</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>2.82625488828223</v>
+        <v>5.297386540190818</v>
       </c>
       <c r="F19" t="n">
-        <v>3.128273790895261</v>
+        <v>5.30206623842959</v>
       </c>
       <c r="G19" t="n">
-        <v>1.341036993249256</v>
+        <v>5.297386540190818</v>
       </c>
       <c r="H19" t="n">
-        <v>4.167291881531487</v>
+        <v>5.520102144718336</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SHERWOOD_FLEET</t>
+          <t>mv_f0_lv_NIMBUS_AMBER</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mv_f0_lv_sherwood_fleet</t>
+          <t>mv_f0_lv_nimbus_amber</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>2.727147560626675</v>
+        <v>5.142212489061682</v>
       </c>
       <c r="F20" t="n">
-        <v>2.728438289872758</v>
+        <v>5.217208207936443</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.727147560626675</v>
+        <v>5.142212489061682</v>
       </c>
       <c r="H20" t="n">
-        <v>2.811062304335735</v>
+        <v>6.023638720970769</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HALLAM_RD_RETIREMENT</t>
+          <t>mv_f0_lv_MALABAR_BYRON</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hallam_rd_retirement</t>
+          <t>mv_f0_lv_malabar_byron</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.518910314922997</v>
+        <v>5.050049643293217</v>
       </c>
       <c r="F21" t="n">
-        <v>2.538639460930062</v>
+        <v>5.108520282767393</v>
       </c>
       <c r="G21" t="n">
-        <v>2.518910314922997</v>
+        <v>5.050049643293217</v>
       </c>
       <c r="H21" t="n">
-        <v>2.834791840127945</v>
+        <v>5.820749377119498</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_TANGERINE</t>
+          <t>mv_f0_lv_RALEIGH_LOWDEN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_tangerine</t>
+          <t>mv_f0_lv_raleigh_lowden</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>2.457581536821828</v>
+        <v>5.032876280598442</v>
       </c>
       <c r="F22" t="n">
-        <v>2.58010549454719</v>
+        <v>5.049865737233756</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.457581536821828</v>
+        <v>5.032876280598442</v>
       </c>
       <c r="H22" t="n">
-        <v>3.243226082952622</v>
+        <v>5.446760694749322</v>
       </c>
     </row>
     <row r="23">
@@ -1112,706 +1112,706 @@
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>1.945170435141205</v>
+        <v>4.777956465710691</v>
       </c>
       <c r="F23" t="n">
-        <v>2.293262935566214</v>
+        <v>5.047832570727388</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.945170435141205</v>
+        <v>4.777956465710691</v>
       </c>
       <c r="H23" t="n">
-        <v>3.159817243845014</v>
+        <v>6.40637461651523</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GERALDINE_PAULINE</t>
+          <t>mv_f0_lv_LESLEY_CARMEN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mv_f0_lv_geraldine_pauline</t>
+          <t>mv_f0_lv_lesley_carmen</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.837754344974178</v>
+        <v>4.345684515739327</v>
       </c>
       <c r="F24" t="n">
-        <v>2.22441779299859</v>
+        <v>4.345751129150246</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.837754344974178</v>
+        <v>4.345684515739327</v>
       </c>
       <c r="H24" t="n">
-        <v>3.09102745381249</v>
+        <v>4.369746231681653</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mv_f0_lv_CORAL_CLAUD</t>
+          <t>mv_f0_lv_HALLAM_EDEYS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mv_f0_lv_coral_claud</t>
+          <t>mv_f0_lv_hallam_edeys</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>1.636432673079453</v>
+        <v>4.300457061566824</v>
       </c>
       <c r="F25" t="n">
-        <v>1.641876271353205</v>
+        <v>4.316161911813976</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.636432673079453</v>
+        <v>4.300457061566824</v>
       </c>
       <c r="H25" t="n">
-        <v>1.770020834646044</v>
+        <v>4.668319414375205</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mv_f0_lv_EDEYS_PIONEER</t>
+          <t>mv_f0_lv_SPRINGFLD_KATHERINE</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mv_f0_lv_edeys_pioneer</t>
+          <t>mv_f0_lv_springfld_katherine</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>1.621260520090678</v>
+        <v>4.279093313528023</v>
       </c>
       <c r="F26" t="n">
-        <v>1.624371067159061</v>
+        <v>4.361576902036861</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.621260520090678</v>
+        <v>4.279093313528023</v>
       </c>
       <c r="H26" t="n">
-        <v>1.721737830060498</v>
+        <v>5.123316913352873</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mv_f0_lv_COMMUNITY_HARRINGTON</t>
+          <t>mv_f0_lv_ORMOND_STRATHAIRD</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mv_f0_lv_community_harrington</t>
+          <t>mv_f0_lv_ormond_strathaird</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.597541056692343</v>
+        <v>4.028795177213718</v>
       </c>
       <c r="F27" t="n">
-        <v>1.610845661490978</v>
+        <v>4.197903758556547</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.597541056692343</v>
+        <v>4.028795177213718</v>
       </c>
       <c r="H27" t="n">
-        <v>1.80414772968869</v>
+        <v>5.208288876290855</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TIMMS_STRATHAIRD</t>
+          <t>mv_f0_lv_OAKGROVE_OXENFORD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mv_f0_lv_timms_strathaird</t>
+          <t>mv_f0_lv_oakgrove_oxenford</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>1.547123563329004</v>
+        <v>3.952848069231433</v>
       </c>
       <c r="F28" t="n">
-        <v>1.967121854490061</v>
+        <v>3.96815284246169</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.547123563329004</v>
+        <v>3.952848069231433</v>
       </c>
       <c r="H28" t="n">
-        <v>2.762021530322357</v>
+        <v>4.301027796829302</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mv_f0_lv_P12_SCHOOL_ORMOND</t>
+          <t>mv_f0_lv_MICHELLE_SIMON</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mv_f0_lv_p12_school_ormond</t>
+          <t>mv_f0_lv_michelle_simon</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>1.505506141546534</v>
+        <v>3.89817969430967</v>
       </c>
       <c r="F29" t="n">
-        <v>1.505523064093401</v>
+        <v>3.962837203101098</v>
       </c>
       <c r="G29" t="n">
-        <v>1.505506141546534</v>
+        <v>3.89817969430967</v>
       </c>
       <c r="H29" t="n">
-        <v>1.512644368416636</v>
+        <v>4.611112909382374</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GREENVIEW_SNOWDONIA</t>
+          <t>mv_f0_lv_KERSHAW_ORMOND</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mv_f0_lv_greenview_snowdonia</t>
+          <t>mv_f0_lv_kershaw_ormond</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.252650202468573</v>
+        <v>3.804851347246053</v>
       </c>
       <c r="F30" t="n">
-        <v>1.26937241859346</v>
+        <v>4.684273111921799</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.252650202468573</v>
+        <v>3.804851347246053</v>
       </c>
       <c r="H30" t="n">
-        <v>1.45801282648096</v>
+        <v>6.537161873601619</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LEOPOLD_HAZEL</t>
+          <t>mv_f0_lv_TIMMS_STRATHAIRD</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mv_f0_lv_leopold_hazel</t>
+          <t>mv_f0_lv_timms_strathaird</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>1.150975600984633</v>
+        <v>3.530775127172703</v>
       </c>
       <c r="F31" t="n">
-        <v>1.27225390209218</v>
+        <v>3.878995877790905</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5421117572298542</v>
+        <v>3.530775127172703</v>
       </c>
       <c r="H31" t="n">
-        <v>1.693087358214488</v>
+        <v>5.137086436121692</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mv_f0_lv_MICHELLE_SIMON</t>
+          <t>mv_f0_lv_HADLEY_CHESTERFIELD</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mv_f0_lv_michelle_simon</t>
+          <t>mv_f0_lv_hadley_chesterfield</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>1.077431736028387</v>
+        <v>3.517246481461083</v>
       </c>
       <c r="F32" t="n">
-        <v>1.507796657786879</v>
+        <v>3.654962467101291</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.054794584472322</v>
+        <v>3.517246481461083</v>
       </c>
       <c r="H32" t="n">
-        <v>2.13222632050071</v>
+        <v>4.511091451548868</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mv_f0_lv_RALEIGH_LOWDEN</t>
+          <t>mv_f0_lv_EDEYS_MOLLISONS</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mv_f0_lv_raleigh_lowden</t>
+          <t>mv_f0_lv_edeys_mollisons</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.060903954401588</v>
+        <v>3.291751593568328</v>
       </c>
       <c r="F33" t="n">
-        <v>1.140070643574751</v>
+        <v>3.300771747166265</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.060903954401588</v>
+        <v>3.291751593568328</v>
       </c>
       <c r="H33" t="n">
-        <v>1.478329243376779</v>
+        <v>3.535607233510099</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LEOPOLD_WENDY</t>
+          <t>mv_f0_lv_SHERWOOD_FLEET</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mv_f0_lv_leopold_wendy</t>
+          <t>mv_f0_lv_sherwood_fleet</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>1.033628907757514</v>
+        <v>3.268164578114149</v>
       </c>
       <c r="F34" t="n">
-        <v>1.046010626100067</v>
+        <v>3.319076537492001</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.1604665415663469</v>
+        <v>3.268164578114149</v>
       </c>
       <c r="H34" t="n">
-        <v>1.194095449323861</v>
+        <v>3.847275406962876</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SALLYS_RUN_ORMOND</t>
+          <t>mv_f0_lv_LESLEY_AMY</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mv_f0_lv_sallys_run_ormond</t>
+          <t>mv_f0_lv_lesley_amy</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>0.980914217063602</v>
+        <v>3.24877018916549</v>
       </c>
       <c r="F35" t="n">
-        <v>1.064943145877004</v>
+        <v>3.322072485403092</v>
       </c>
       <c r="G35" t="n">
-        <v>0.980914217063602</v>
+        <v>3.24877018916549</v>
       </c>
       <c r="H35" t="n">
-        <v>1.395535975673676</v>
+        <v>3.942785935573241</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mv_f0_lv_OAKGROVE_OXENFORD</t>
+          <t>mv_f0_lv_COMMUNITY_HARRINGTON</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mv_f0_lv_oakgrove_oxenford</t>
+          <t>mv_f0_lv_community_harrington</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9759697003584664</v>
+        <v>3.171313186291137</v>
       </c>
       <c r="F36" t="n">
-        <v>1.000947634826168</v>
+        <v>3.183808790880531</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9759697003584664</v>
+        <v>3.171313186291137</v>
       </c>
       <c r="H36" t="n">
-        <v>1.198184262541744</v>
+        <v>3.453112922529666</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TANGERINE_NORWEGIAN</t>
+          <t>mv_f0_lv_CHISHOLM_KERSHAW</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mv_f0_lv_tangerine_norwegian</t>
+          <t>mv_f0_lv_chisholm_kershaw</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9129788600518012</v>
+        <v>2.788889228433991</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9690682018862853</v>
+        <v>2.799097877337304</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.3249042643697244</v>
+        <v>2.788889228433991</v>
       </c>
       <c r="H37" t="n">
-        <v>1.237883124421526</v>
+        <v>3.027731851177627</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LESLEY_CARMEN</t>
+          <t>mv_f0_lv_HALLAM_RD_RETIREMENT</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>mv_f0_lv_lesley_carmen</t>
+          <t>mv_f0_lv_hallam_rd_retirement</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8402401250605598</v>
+        <v>2.365045981866977</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8931587899023001</v>
+        <v>2.461922019787919</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.8402401250605598</v>
+        <v>2.365045981866977</v>
       </c>
       <c r="H38" t="n">
-        <v>1.14310834098616</v>
+        <v>3.048871643254067</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mv_f0_lv_MALABAR_BYRON</t>
+          <t>mv_f0_lv_VIEWSIDE_NEESAN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mv_f0_lv_malabar_byron</t>
+          <t>mv_f0_lv_viewside_neesan</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7806554691151302</v>
+        <v>2.04314893800816</v>
       </c>
       <c r="F39" t="n">
-        <v>1.050619170369556</v>
+        <v>2.104416910560541</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7031199610938739</v>
+        <v>2.04314893800816</v>
       </c>
       <c r="H39" t="n">
-        <v>1.483775430209004</v>
+        <v>2.547245109952858</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HADLEY_CHESTERFIELD</t>
+          <t>mv_f0_lv_BARINGA_PARK_CASPIAN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hadley_chesterfield</t>
+          <t>mv_f0_lv_baringa_park_caspian</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6527336436366271</v>
+        <v>1.933007051992911</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9173446317393896</v>
+        <v>2.402135026483953</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6445618386515983</v>
+        <v>1.933007051992911</v>
       </c>
       <c r="H40" t="n">
-        <v>1.297295482288225</v>
+        <v>3.35909836127389</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_STRATHAIRD</t>
+          <t>mv_f0_lv_SPRINGFIELD_HUNTNGTN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_strathaird</t>
+          <t>mv_f0_lv_springfield_huntngtn</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>0.646458534197043</v>
+        <v>1.918467312805287</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8291307877342984</v>
+        <v>1.918942891843919</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5191813042981313</v>
+        <v>1.918467312805287</v>
       </c>
       <c r="H41" t="n">
-        <v>1.165639838495174</v>
+        <v>1.961187236213034</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>mv_f0_lv_BARINGA_PARK_CASPIAN</t>
+          <t>mv_f0_lv_THE_PARKWAY_KARKALLA</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mv_f0_lv_baringa_park_caspian</t>
+          <t>mv_f0_lv_the_parkway_karkalla</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6178875274035853</v>
+        <v>1.756843051015878</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6179649474139653</v>
+        <v>2.441051062629912</v>
       </c>
       <c r="G42" t="n">
-        <v>0.009781600657788658</v>
+        <v>-1.756843051015878</v>
       </c>
       <c r="H42" t="n">
-        <v>0.627669128061374</v>
+        <v>3.45160934300538</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFIELD_JANET</t>
+          <t>mv_f0_lv_ORMOND_SCHOOL</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfield_janet</t>
+          <t>mv_f0_lv_ormond_school</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4463374927275385</v>
+        <v>1.578680583181973</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6118886757734596</v>
+        <v>1.594729311459841</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.41855775482661</v>
+        <v>1.578680583181973</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8648952475541485</v>
+        <v>1.804355555461587</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_SCHOOL</t>
+          <t>mv_f0_lv_LEOPOLD_WENDY</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_school</t>
+          <t>mv_f0_lv_leopold_wendy</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2504477928385813</v>
+        <v>1.56819091085003</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3210478139697901</v>
+        <v>1.576109800787334</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2504477928385813</v>
+        <v>1.56819091085003</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4513149178667053</v>
+        <v>1.725986256995736</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mv_f0_lv_VIEWSIDE_NEESAN</t>
+          <t>mv_f0_lv_SALLYS_RUN_ORMOND</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mv_f0_lv_viewside_neesan</t>
+          <t>mv_f0_lv_sallys_run_ormond</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2283263850320827</v>
+        <v>1.43671286136442</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3140703230616121</v>
+        <v>1.444117217402911</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.2283263850320827</v>
+        <v>1.43671286136442</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4439817344352601</v>
+        <v>1.58276316636098</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFIELD_HUNTNGTN</t>
+          <t>mv_f0_lv_P12_SCHOOL_ORMOND</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfield_huntngtn</t>
+          <t>mv_f0_lv_p12_school_ormond</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>0.209675671797898</v>
+        <v>1.297204486817126</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2176202948360347</v>
+        <v>1.403701136360668</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.209675671797898</v>
+        <v>-1.297204486817126</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2679397720709034</v>
+        <v>1.833522862040041</v>
       </c>
     </row>
   </sheetData>
@@ -2060,139 +2060,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.517864426795253</v>
+        <v>4.284135886578531</v>
       </c>
       <c r="C2" t="n">
-        <v>1.198184262541744</v>
+        <v>3.604668341633563</v>
       </c>
       <c r="D2" t="n">
-        <v>-8.189533077993048</v>
+        <v>10.87717908037843</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.45801282648096</v>
+        <v>6.115992751759915</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.687720040634836</v>
+        <v>1.072540820890488</v>
       </c>
       <c r="G2" t="n">
-        <v>1.483775430209004</v>
+        <v>4.279349909466937</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.548926449673321</v>
+        <v>3.027731851177627</v>
       </c>
       <c r="I2" t="n">
-        <v>1.512644368416636</v>
+        <v>-0.7608861115942105</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4513149178667053</v>
+        <v>1.804355555461587</v>
       </c>
       <c r="K2" t="n">
-        <v>0.627669128061374</v>
+        <v>0.5069157427119322</v>
       </c>
       <c r="L2" t="n">
-        <v>-6.514360814124345</v>
+        <v>8.487403622643718</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.527669914317848</v>
+        <v>3.932594708758444</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1272772298989118</v>
+        <v>2.849301478136582</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.811062304335735</v>
+        <v>2.689053749265423</v>
       </c>
       <c r="P2" t="n">
-        <v>-6.336204108915759</v>
+        <v>5.520102144718336</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.520783210120857</v>
+        <v>11.0603186085347</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.80414772968869</v>
+        <v>3.453112922529666</v>
       </c>
       <c r="S2" t="n">
-        <v>-5.74158147101322</v>
+        <v>3.434869713703172</v>
       </c>
       <c r="T2" t="n">
-        <v>-5.213071355438331</v>
+        <v>8.806721057119923</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8648952475541485</v>
+        <v>3.825432600978033</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1514115715248927</v>
+        <v>1.87574738939754</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6434786654263966</v>
+        <v>5.446760694749322</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8731623661911669</v>
+        <v>1.725986256995736</v>
       </c>
       <c r="Y2" t="n">
-        <v>-3.515419349489672</v>
+        <v>5.630383361263199</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.167291881531487</v>
+        <v>9.139401762027056</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.834791840127945</v>
+        <v>3.048871643254067</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.3322255963356504</v>
+        <v>1.924463818223714</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.502844511512862</v>
+        <v>6.708628956944892</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.02263715155606505</v>
+        <v>3.185246479236966</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.6088638437547793</v>
+        <v>6.397113355207807</v>
       </c>
       <c r="AF2" t="n">
-        <v>-3.863006592956083</v>
+        <v>4.260786257152596</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3.09102745381249</v>
+        <v>5.249957860836187</v>
       </c>
       <c r="AH2" t="n">
-        <v>-3.469970121426439</v>
+        <v>-3.45160934300538</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1.14310834098616</v>
+        <v>4.321622799797002</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.4439817344352601</v>
+        <v>1.539052766063463</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.395535975673676</v>
+        <v>1.29066255636786</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.432992242648057</v>
+        <v>2.554754442757739</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2.481910745657281</v>
+        <v>6.213166199657014</v>
       </c>
       <c r="AN2" t="n">
-        <v>-3.214159804373079</v>
+        <v>5.673608087326713</v>
       </c>
       <c r="AO2" t="n">
-        <v>-5.39665799716429</v>
+        <v>3.535607233510099</v>
       </c>
       <c r="AP2" t="n">
-        <v>-3.243226082952622</v>
+        <v>5.085041109006529</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-4.42294661355626</v>
+        <v>9.131211298030582</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.730523626437396</v>
+        <v>3.149538314906152</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.5880745956820768</v>
+        <v>7.755815650100864</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.008171804985028785</v>
+        <v>2.523401511373297</v>
       </c>
     </row>
     <row r="3">
@@ -2200,139 +2200,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-2.16306720659321</v>
+        <v>4.785749591300761</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7537551381751886</v>
+        <v>4.301027796829302</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.447092101723239</v>
+        <v>9.800230809176639</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.047287578456185</v>
+        <v>4.552437269091552</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.857184906443489</v>
+        <v>6.537161873601619</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.07753550802125631</v>
+        <v>5.820749377119498</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.923426068510512</v>
+        <v>2.550046605690355</v>
       </c>
       <c r="I3" t="n">
-        <v>1.498367914676432</v>
+        <v>-1.833522862040041</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04958066781045734</v>
+        <v>1.353005610902359</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6081059267457967</v>
+        <v>3.35909836127389</v>
       </c>
       <c r="L3" t="n">
-        <v>-8.688255942402883</v>
+        <v>8.644811506173951</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.256358302054871</v>
+        <v>4.668319414375205</v>
       </c>
       <c r="N3" t="n">
-        <v>1.165639838495174</v>
+        <v>5.208288876290855</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.643232816917616</v>
+        <v>3.847275406962876</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.933981388425085</v>
+        <v>5.074670935663299</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.721737830060498</v>
+        <v>4.061202773697545</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.390934383695996</v>
+        <v>2.889513450052608</v>
       </c>
       <c r="S3" t="n">
-        <v>-6.223773927755985</v>
+        <v>5.123316913352873</v>
       </c>
       <c r="T3" t="n">
-        <v>-6.329728179725372</v>
+        <v>6.475945397805141</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02777973790092858</v>
+        <v>7.290221048335489</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2679397720709034</v>
+        <v>1.961187236213034</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.478329243376779</v>
+        <v>4.618991866447562</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.194095449323861</v>
+        <v>1.410395564704324</v>
       </c>
       <c r="Y3" t="n">
-        <v>-5.093584341907388</v>
+        <v>6.402810891630764</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.485217895032974</v>
+        <v>6.018027849962408</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.203028789718049</v>
+        <v>1.681220320479888</v>
       </c>
       <c r="AB3" t="n">
-        <v>-2.762021530322357</v>
+        <v>5.137086436121692</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.770020834646044</v>
+        <v>6.777218044954516</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2.13222632050071</v>
+        <v>4.611112909382374</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1.693087358214488</v>
+        <v>5.800318494405289</v>
       </c>
       <c r="AF3" t="n">
-        <v>-4.063192436680399</v>
+        <v>6.023638720970769</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.5844812361358667</v>
+        <v>7.592144626623679</v>
       </c>
       <c r="AH3" t="n">
-        <v>-7.010918068270229</v>
+        <v>-0.06207675902637533</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.5373719091349596</v>
+        <v>4.369746231681653</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.01267103562890526</v>
+        <v>2.547245109952858</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.5662924584535283</v>
+        <v>1.58276316636098</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.829680146553354</v>
+        <v>3.942785935573241</v>
       </c>
       <c r="AM3" t="n">
-        <v>-3.311793797706731</v>
+        <v>6.127938363758965</v>
       </c>
       <c r="AN3" t="n">
-        <v>-2.789217596334773</v>
+        <v>5.606788892959372</v>
       </c>
       <c r="AO3" t="n">
-        <v>-2.489472963959766</v>
+        <v>3.047895953626558</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1.671936990691034</v>
+        <v>6.889903350395919</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-4.077872290452671</v>
+        <v>8.27609853201178</v>
       </c>
       <c r="AR3" t="n">
-        <v>-3.159817243845014</v>
+        <v>6.40637461651523</v>
       </c>
       <c r="AS3" t="n">
-        <v>-1.237883124421526</v>
+        <v>9.568473645623165</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1.297295482288225</v>
+        <v>4.511091451548868</v>
       </c>
     </row>
   </sheetData>

--- a/nando/Nando_final/metrics/net_3_Urban_HPK11/trafo_loading_compare.xlsx
+++ b/nando/Nando_final/metrics/net_3_Urban_HPK11/trafo_loading_compare.xlsx
@@ -482,136 +482,136 @@
         <v>88</v>
       </c>
       <c r="E2" t="n">
-        <v>4.673763081568418</v>
+        <v>14.87386871262336</v>
       </c>
       <c r="F2" t="n">
-        <v>4.795306402115677</v>
+        <v>14.89142818982848</v>
       </c>
       <c r="G2" t="n">
-        <v>4.534942738939646</v>
+        <v>14.87386871262336</v>
       </c>
       <c r="H2" t="n">
-        <v>11.0603186085347</v>
+        <v>24.81343692019105</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mv_f0_lv_CHATSWOOD_FLEET</t>
+          <t>mv_f0_lv_KERSHAW_ORMOND</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mv_f0_lv_chatswood_fleet</t>
+          <t>mv_f0_lv_kershaw_ormond</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>10.33870494477754</v>
+        <v>22.88560020706302</v>
       </c>
       <c r="F3" t="n">
-        <v>10.35271820972051</v>
+        <v>22.96665520335966</v>
       </c>
       <c r="G3" t="n">
-        <v>10.33870494477754</v>
+        <v>22.88560020706302</v>
       </c>
       <c r="H3" t="n">
-        <v>10.87717908037843</v>
+        <v>24.81343692019105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HIGHMOUNT_ORMOND</t>
+          <t>mv_f0_lv_TANGERINE_NORWEGIAN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mv_f0_lv_highmount_ormond</t>
+          <t>mv_f0_lv_tangerine_norwegian</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>8.703654915021181</v>
+        <v>21.38868796980015</v>
       </c>
       <c r="F4" t="n">
-        <v>8.714150178900088</v>
+        <v>21.4003048334307</v>
       </c>
       <c r="G4" t="n">
-        <v>8.703654915021181</v>
+        <v>21.38868796980015</v>
       </c>
       <c r="H4" t="n">
-        <v>9.131211298030582</v>
+        <v>22.09372264574459</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TANGERINE_NORWEGIAN</t>
+          <t>mv_f0_lv_CHATSWOOD_FLEET</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mv_f0_lv_tangerine_norwegian</t>
+          <t>mv_f0_lv_chatswood_fleet</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>8.662144647862014</v>
+        <v>21.30519337063403</v>
       </c>
       <c r="F5" t="n">
-        <v>8.709430644575297</v>
+        <v>21.31462037244255</v>
       </c>
       <c r="G5" t="n">
-        <v>8.662144647862014</v>
+        <v>21.30519337063403</v>
       </c>
       <c r="H5" t="n">
-        <v>9.568473645623165</v>
+        <v>21.93905223602511</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TUILERIES_PROVENCE</t>
+          <t>mv_f0_lv_GOLDEN_CHERRYWOOD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mv_f0_lv_tuileries_provence</t>
+          <t>mv_f0_lv_golden_cherrywood</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>8.566107564408835</v>
+        <v>21.27170938340344</v>
       </c>
       <c r="F6" t="n">
-        <v>8.566469116005242</v>
+        <v>21.3204346869026</v>
       </c>
       <c r="G6" t="n">
-        <v>8.566107564408835</v>
+        <v>21.27170938340344</v>
       </c>
       <c r="H6" t="n">
-        <v>8.644811506173951</v>
+        <v>22.71230479728805</v>
       </c>
     </row>
     <row r="7">
@@ -632,646 +632,646 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>7.641333227462532</v>
+        <v>21.20127886427439</v>
       </c>
       <c r="F7" t="n">
-        <v>7.729689663022477</v>
+        <v>21.20325764516043</v>
       </c>
       <c r="G7" t="n">
-        <v>7.641333227462532</v>
+        <v>21.20127886427439</v>
       </c>
       <c r="H7" t="n">
-        <v>8.806721057119923</v>
+        <v>21.49094986096896</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mv_f0_lv_VON_NIDA_DULWICH</t>
+          <t>mv_f0_lv_HALLAM_EDEYS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mv_f0_lv_von_nida_dulwich</t>
+          <t>mv_f0_lv_hallam_edeys</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>7.578714805994732</v>
+        <v>20.05831222990656</v>
       </c>
       <c r="F8" t="n">
-        <v>7.737742686684096</v>
+        <v>20.05887003371603</v>
       </c>
       <c r="G8" t="n">
-        <v>7.578714805994732</v>
+        <v>20.05831222990656</v>
       </c>
       <c r="H8" t="n">
-        <v>9.139401762027056</v>
+        <v>20.20790339639703</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mv_f0_lv_EDEYS_PIONEER</t>
+          <t>mv_f0_lv_TUILERIES_PROVENCE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mv_f0_lv_edeys_pioneer</t>
+          <t>mv_f0_lv_tuileries_provence</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>7.560760691116123</v>
+        <v>19.70809232740478</v>
       </c>
       <c r="F9" t="n">
-        <v>8.331386910094489</v>
+        <v>19.71104602076068</v>
       </c>
       <c r="G9" t="n">
-        <v>7.560760691116123</v>
+        <v>19.70809232740478</v>
       </c>
       <c r="H9" t="n">
-        <v>11.0603186085347</v>
+        <v>20.04931373211755</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mv_f0_lv_CORAL_CLAUD</t>
+          <t>mv_f0_lv_THE_PARKWAY_KARKALLA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mv_f0_lv_coral_claud</t>
+          <t>mv_f0_lv_the_parkway_karkalla</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>6.742923500949704</v>
+        <v>19.12418956861428</v>
       </c>
       <c r="F10" t="n">
-        <v>6.743010711500339</v>
+        <v>19.12532304464188</v>
       </c>
       <c r="G10" t="n">
-        <v>6.742923500949704</v>
+        <v>19.12418956861428</v>
       </c>
       <c r="H10" t="n">
-        <v>6.777218044954516</v>
+        <v>19.33240797705709</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GERALDINE_PAULINE</t>
+          <t>mv_f0_lv_NORWEGIAN_GLASSCOCKS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mv_f0_lv_geraldine_pauline</t>
+          <t>mv_f0_lv_norwegian_glasscocks</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>6.421051243729933</v>
+        <v>18.82154652955494</v>
       </c>
       <c r="F11" t="n">
-        <v>6.526971639747122</v>
+        <v>18.82157546120268</v>
       </c>
       <c r="G11" t="n">
-        <v>6.421051243729933</v>
+        <v>18.82154652955494</v>
       </c>
       <c r="H11" t="n">
-        <v>7.592144626623679</v>
+        <v>18.85454770446196</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TOOMAH_STRATHARD</t>
+          <t>mv_f0_lv_CHISHOLM_KERSHAW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mv_f0_lv_toomah_strathard</t>
+          <t>mv_f0_lv_chisholm_kershaw</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>6.170552281707989</v>
+        <v>18.03000089769731</v>
       </c>
       <c r="F12" t="n">
-        <v>6.170699426101926</v>
+        <v>18.03321835279163</v>
       </c>
       <c r="G12" t="n">
-        <v>6.170552281707989</v>
+        <v>18.03000089769731</v>
       </c>
       <c r="H12" t="n">
-        <v>6.213166199657014</v>
+        <v>18.37063528893662</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LEOPOLD_HAZEL</t>
+          <t>mv_f0_lv_CORAL_CLAUD</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mv_f0_lv_leopold_hazel</t>
+          <t>mv_f0_lv_coral_claud</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>6.098715924806548</v>
+        <v>17.87824915160074</v>
       </c>
       <c r="F13" t="n">
-        <v>6.106011542566806</v>
+        <v>17.92051847903733</v>
       </c>
       <c r="G13" t="n">
-        <v>6.098715924806548</v>
+        <v>17.87824915160074</v>
       </c>
       <c r="H13" t="n">
-        <v>6.397113355207807</v>
+        <v>19.10836696335945</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mv_f0_lv_NORWEGIAN_GLASSCOCKS</t>
+          <t>mv_f0_lv_PARKWAY_REDWOOD</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mv_f0_lv_norwegian_glasscocks</t>
+          <t>mv_f0_lv_parkway_redwood</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>6.016597126446982</v>
+        <v>17.76821338781283</v>
       </c>
       <c r="F14" t="n">
-        <v>6.02898018361211</v>
+        <v>17.79186370470276</v>
       </c>
       <c r="G14" t="n">
-        <v>6.016597126446982</v>
+        <v>17.76821338781283</v>
       </c>
       <c r="H14" t="n">
-        <v>6.402810891630764</v>
+        <v>18.68527777588395</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_TANGERINE</t>
+          <t>mv_f0_lv_TOOMAH_STRATHARD</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_tangerine</t>
+          <t>mv_f0_lv_toomah_strathard</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.987472229701224</v>
+        <v>17.47593716384758</v>
       </c>
       <c r="F15" t="n">
-        <v>6.055097491291253</v>
+        <v>17.47786607072911</v>
       </c>
       <c r="G15" t="n">
-        <v>5.987472229701224</v>
+        <v>17.47593716384758</v>
       </c>
       <c r="H15" t="n">
-        <v>6.889903350395919</v>
+        <v>17.73559584672712</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mv_f0_lv_JESSICA_GERALDINE</t>
+          <t>mv_f0_lv_LEOPOLD_HAZEL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mv_f0_lv_jessica_geraldine</t>
+          <t>mv_f0_lv_leopold_hazel</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>5.640198490143042</v>
+        <v>17.31910592200818</v>
       </c>
       <c r="F16" t="n">
-        <v>5.640297439798351</v>
+        <v>17.33764254272581</v>
       </c>
       <c r="G16" t="n">
-        <v>5.640198490143042</v>
+        <v>17.31910592200818</v>
       </c>
       <c r="H16" t="n">
-        <v>5.673608087326713</v>
+        <v>18.12061637209431</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFIELD_JANET</t>
+          <t>mv_f0_lv_SPRINGFLD_KATHERINE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfield_janet</t>
+          <t>mv_f0_lv_springfld_katherine</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>5.557826824656761</v>
+        <v>17.20735583854744</v>
       </c>
       <c r="F17" t="n">
-        <v>5.82156583395822</v>
+        <v>17.2198850252475</v>
       </c>
       <c r="G17" t="n">
-        <v>5.557826824656761</v>
+        <v>17.20735583854744</v>
       </c>
       <c r="H17" t="n">
-        <v>7.290221048335489</v>
+        <v>17.86412469313048</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GREENVIEW_SNOWDONIA</t>
+          <t>mv_f0_lv_MALABAR_BYRON</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mv_f0_lv_greenview_snowdonia</t>
+          <t>mv_f0_lv_malabar_byron</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.334215010425734</v>
+        <v>16.95771732513396</v>
       </c>
       <c r="F18" t="n">
-        <v>5.391198958886306</v>
+        <v>16.95952073651088</v>
       </c>
       <c r="G18" t="n">
-        <v>5.334215010425734</v>
+        <v>16.95771732513396</v>
       </c>
       <c r="H18" t="n">
-        <v>6.115992751759915</v>
+        <v>17.20503641658092</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GOLDEN_CHERRYWOOD</t>
+          <t>mv_f0_lv_EDEYS_MOLLISONS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mv_f0_lv_golden_cherrywood</t>
+          <t>mv_f0_lv_edeys_mollisons</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>5.297386540190818</v>
+        <v>16.91075122215157</v>
       </c>
       <c r="F19" t="n">
-        <v>5.30206623842959</v>
+        <v>16.91891386458051</v>
       </c>
       <c r="G19" t="n">
-        <v>5.297386540190818</v>
+        <v>16.91075122215157</v>
       </c>
       <c r="H19" t="n">
-        <v>5.520102144718336</v>
+        <v>17.43624095525147</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mv_f0_lv_NIMBUS_AMBER</t>
+          <t>mv_f0_lv_COMMUNITY_HARRINGTON</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mv_f0_lv_nimbus_amber</t>
+          <t>mv_f0_lv_community_harrington</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>5.142212489061682</v>
+        <v>16.81034397169681</v>
       </c>
       <c r="F20" t="n">
-        <v>5.217208207936443</v>
+        <v>16.82997143625323</v>
       </c>
       <c r="G20" t="n">
-        <v>5.142212489061682</v>
+        <v>16.81034397169681</v>
       </c>
       <c r="H20" t="n">
-        <v>6.023638720970769</v>
+        <v>17.62291649051376</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mv_f0_lv_MALABAR_BYRON</t>
+          <t>mv_f0_lv_BARINGA_PARK_CASPIAN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mv_f0_lv_malabar_byron</t>
+          <t>mv_f0_lv_baringa_park_caspian</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.050049643293217</v>
+        <v>16.36347669332461</v>
       </c>
       <c r="F21" t="n">
-        <v>5.108520282767393</v>
+        <v>16.36353663154562</v>
       </c>
       <c r="G21" t="n">
-        <v>5.050049643293217</v>
+        <v>16.36347669332461</v>
       </c>
       <c r="H21" t="n">
-        <v>5.820749377119498</v>
+        <v>16.40776663526857</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mv_f0_lv_RALEIGH_LOWDEN</t>
+          <t>mv_f0_lv_VON_NIDA_DULWICH</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mv_f0_lv_raleigh_lowden</t>
+          <t>mv_f0_lv_von_nida_dulwich</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>5.032876280598442</v>
+        <v>15.88059623638382</v>
       </c>
       <c r="F22" t="n">
-        <v>5.049865737233756</v>
+        <v>15.94027776584066</v>
       </c>
       <c r="G22" t="n">
-        <v>5.032876280598442</v>
+        <v>15.88059623638382</v>
       </c>
       <c r="H22" t="n">
-        <v>5.446760694749322</v>
+        <v>17.25868129511795</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mv_f0_lv_PARKWAY_REDWOOD</t>
+          <t>mv_f0_lv_EDEYS_PIONEER</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mv_f0_lv_parkway_redwood</t>
+          <t>mv_f0_lv_edeys_pioneer</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>4.777956465710691</v>
+        <v>15.86751886497496</v>
       </c>
       <c r="F23" t="n">
-        <v>5.047832570727388</v>
+        <v>15.89380555207765</v>
       </c>
       <c r="G23" t="n">
-        <v>4.777956465710691</v>
+        <v>15.86751886497496</v>
       </c>
       <c r="H23" t="n">
-        <v>6.40637461651523</v>
+        <v>16.78124748820939</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LESLEY_CARMEN</t>
+          <t>mv_f0_lv_HIGHMOUNT_ORMOND</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mv_f0_lv_lesley_carmen</t>
+          <t>mv_f0_lv_highmount_ormond</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.345684515739327</v>
+        <v>15.6648950373916</v>
       </c>
       <c r="F24" t="n">
-        <v>4.345751129150246</v>
+        <v>15.67551619901469</v>
       </c>
       <c r="G24" t="n">
-        <v>4.345684515739327</v>
+        <v>15.6648950373916</v>
       </c>
       <c r="H24" t="n">
-        <v>4.369746231681653</v>
+        <v>16.24184527187982</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HALLAM_EDEYS</t>
+          <t>mv_f0_lv_NIMBUS_AMBER</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hallam_edeys</t>
+          <t>mv_f0_lv_nimbus_amber</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>4.300457061566824</v>
+        <v>15.46832963916523</v>
       </c>
       <c r="F25" t="n">
-        <v>4.316161911813976</v>
+        <v>15.47648156388161</v>
       </c>
       <c r="G25" t="n">
-        <v>4.300457061566824</v>
+        <v>15.46832963916523</v>
       </c>
       <c r="H25" t="n">
-        <v>4.668319414375205</v>
+        <v>15.97058432683876</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFLD_KATHERINE</t>
+          <t>mv_f0_lv_RALEIGH_LOWDEN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfld_katherine</t>
+          <t>mv_f0_lv_raleigh_lowden</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>4.279093313528023</v>
+        <v>15.19850443902435</v>
       </c>
       <c r="F26" t="n">
-        <v>4.361576902036861</v>
+        <v>15.2082592922748</v>
       </c>
       <c r="G26" t="n">
-        <v>4.279093313528023</v>
+        <v>15.19850443902435</v>
       </c>
       <c r="H26" t="n">
-        <v>5.123316913352873</v>
+        <v>15.74312680178592</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_STRATHAIRD</t>
+          <t>mv_f0_lv_TIMMS_STRATHAIRD</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_strathaird</t>
+          <t>mv_f0_lv_timms_strathaird</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.028795177213718</v>
+        <v>14.94167461940715</v>
       </c>
       <c r="F27" t="n">
-        <v>4.197903758556547</v>
+        <v>14.98072584946505</v>
       </c>
       <c r="G27" t="n">
-        <v>4.028795177213718</v>
+        <v>14.94167461940715</v>
       </c>
       <c r="H27" t="n">
-        <v>5.208288876290855</v>
+        <v>16.02264943159969</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mv_f0_lv_OAKGROVE_OXENFORD</t>
+          <t>mv_f0_lv_ORMOND_STRATHAIRD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mv_f0_lv_oakgrove_oxenford</t>
+          <t>mv_f0_lv_ormond_strathaird</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>3.952848069231433</v>
+        <v>14.72209371942135</v>
       </c>
       <c r="F28" t="n">
-        <v>3.96815284246169</v>
+        <v>14.72219176669004</v>
       </c>
       <c r="G28" t="n">
-        <v>3.952848069231433</v>
+        <v>14.72209371942135</v>
       </c>
       <c r="H28" t="n">
-        <v>4.301027796829302</v>
+        <v>14.7758238950241</v>
       </c>
     </row>
     <row r="29">
@@ -1292,496 +1292,496 @@
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>3.89817969430967</v>
+        <v>14.56737870681676</v>
       </c>
       <c r="F29" t="n">
-        <v>3.962837203101098</v>
+        <v>14.57793620931303</v>
       </c>
       <c r="G29" t="n">
-        <v>3.89817969430967</v>
+        <v>14.56737870681676</v>
       </c>
       <c r="H29" t="n">
-        <v>4.611112909382374</v>
+        <v>15.12208740062074</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mv_f0_lv_KERSHAW_ORMOND</t>
+          <t>mv_f0_lv_GREENVIEW_SNOWDONIA</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mv_f0_lv_kershaw_ormond</t>
+          <t>mv_f0_lv_greenview_snowdonia</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.804851347246053</v>
+        <v>14.46506340270242</v>
       </c>
       <c r="F30" t="n">
-        <v>4.684273111921799</v>
+        <v>14.47339448080334</v>
       </c>
       <c r="G30" t="n">
-        <v>3.804851347246053</v>
+        <v>14.46506340270242</v>
       </c>
       <c r="H30" t="n">
-        <v>6.537161873601619</v>
+        <v>14.95607109383139</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TIMMS_STRATHAIRD</t>
+          <t>mv_f0_lv_JESSICA_GERALDINE</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mv_f0_lv_timms_strathaird</t>
+          <t>mv_f0_lv_jessica_geraldine</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>3.530775127172703</v>
+        <v>14.06576313770996</v>
       </c>
       <c r="F31" t="n">
-        <v>3.878995877790905</v>
+        <v>14.1006869315421</v>
       </c>
       <c r="G31" t="n">
-        <v>3.530775127172703</v>
+        <v>14.06576313770996</v>
       </c>
       <c r="H31" t="n">
-        <v>5.137086436121692</v>
+        <v>15.05756921512721</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HADLEY_CHESTERFIELD</t>
+          <t>mv_f0_lv_LESLEY_CARMEN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hadley_chesterfield</t>
+          <t>mv_f0_lv_lesley_carmen</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>3.517246481461083</v>
+        <v>13.57116806318338</v>
       </c>
       <c r="F32" t="n">
-        <v>3.654962467101291</v>
+        <v>13.63082118132578</v>
       </c>
       <c r="G32" t="n">
-        <v>3.517246481461083</v>
+        <v>13.57116806318338</v>
       </c>
       <c r="H32" t="n">
-        <v>4.511091451548868</v>
+        <v>14.84501400289153</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mv_f0_lv_EDEYS_MOLLISONS</t>
+          <t>mv_f0_lv_HADLEY_CHESTERFIELD</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mv_f0_lv_edeys_mollisons</t>
+          <t>mv_f0_lv_hadley_chesterfield</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.291751593568328</v>
+        <v>13.1264526501069</v>
       </c>
       <c r="F33" t="n">
-        <v>3.300771747166265</v>
+        <v>13.1308956674946</v>
       </c>
       <c r="G33" t="n">
-        <v>3.291751593568328</v>
+        <v>13.1264526501069</v>
       </c>
       <c r="H33" t="n">
-        <v>3.535607233510099</v>
+        <v>13.46801063219757</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SHERWOOD_FLEET</t>
+          <t>mv_f0_lv_SPRINGFIELD_JANET</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mv_f0_lv_sherwood_fleet</t>
+          <t>mv_f0_lv_springfield_janet</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>3.268164578114149</v>
+        <v>12.65513815914379</v>
       </c>
       <c r="F34" t="n">
-        <v>3.319076537492001</v>
+        <v>12.76836748306578</v>
       </c>
       <c r="G34" t="n">
-        <v>3.268164578114149</v>
+        <v>12.65513815914379</v>
       </c>
       <c r="H34" t="n">
-        <v>3.847275406962876</v>
+        <v>14.35180735365237</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LESLEY_AMY</t>
+          <t>mv_f0_lv_GERALDINE_PAULINE</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mv_f0_lv_lesley_amy</t>
+          <t>mv_f0_lv_geraldine_pauline</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>3.24877018916549</v>
+        <v>12.65393358866355</v>
       </c>
       <c r="F35" t="n">
-        <v>3.322072485403092</v>
+        <v>12.65956023267077</v>
       </c>
       <c r="G35" t="n">
-        <v>3.24877018916549</v>
+        <v>12.65393358866355</v>
       </c>
       <c r="H35" t="n">
-        <v>3.942785935573241</v>
+        <v>13.0313326060332</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mv_f0_lv_COMMUNITY_HARRINGTON</t>
+          <t>mv_f0_lv_LEOPOLD_WENDY</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mv_f0_lv_community_harrington</t>
+          <t>mv_f0_lv_leopold_wendy</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.171313186291137</v>
+        <v>11.62889741284973</v>
       </c>
       <c r="F36" t="n">
-        <v>3.183808790880531</v>
+        <v>11.63472228708444</v>
       </c>
       <c r="G36" t="n">
-        <v>3.171313186291137</v>
+        <v>11.62889741284973</v>
       </c>
       <c r="H36" t="n">
-        <v>3.453112922529666</v>
+        <v>11.99701106241501</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mv_f0_lv_CHISHOLM_KERSHAW</t>
+          <t>mv_f0_lv_SHERWOOD_FLEET</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mv_f0_lv_chisholm_kershaw</t>
+          <t>mv_f0_lv_sherwood_fleet</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>2.788889228433991</v>
+        <v>11.01196268439558</v>
       </c>
       <c r="F37" t="n">
-        <v>2.799097877337304</v>
+        <v>11.01827718203573</v>
       </c>
       <c r="G37" t="n">
-        <v>2.788889228433991</v>
+        <v>11.01196268439558</v>
       </c>
       <c r="H37" t="n">
-        <v>3.027731851177627</v>
+        <v>11.38493707714738</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HALLAM_RD_RETIREMENT</t>
+          <t>mv_f0_lv_OAKGROVE_OXENFORD</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hallam_rd_retirement</t>
+          <t>mv_f0_lv_oakgrove_oxenford</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>2.365045981866977</v>
+        <v>10.88070193362858</v>
       </c>
       <c r="F38" t="n">
-        <v>2.461922019787919</v>
+        <v>10.92650122400274</v>
       </c>
       <c r="G38" t="n">
-        <v>2.365045981866977</v>
+        <v>10.88070193362858</v>
       </c>
       <c r="H38" t="n">
-        <v>3.048871643254067</v>
+        <v>11.8800789544094</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mv_f0_lv_VIEWSIDE_NEESAN</t>
+          <t>mv_f0_lv_ORMOND_TANGERINE</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mv_f0_lv_viewside_neesan</t>
+          <t>mv_f0_lv_ormond_tangerine</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.04314893800816</v>
+        <v>10.11807503116906</v>
       </c>
       <c r="F39" t="n">
-        <v>2.104416910560541</v>
+        <v>10.12335483724872</v>
       </c>
       <c r="G39" t="n">
-        <v>2.04314893800816</v>
+        <v>10.11807503116906</v>
       </c>
       <c r="H39" t="n">
-        <v>2.547245109952858</v>
+        <v>10.44498606567276</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mv_f0_lv_BARINGA_PARK_CASPIAN</t>
+          <t>mv_f0_lv_VIEWSIDE_NEESAN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mv_f0_lv_baringa_park_caspian</t>
+          <t>mv_f0_lv_viewside_neesan</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>1.933007051992911</v>
+        <v>9.740501172121165</v>
       </c>
       <c r="F40" t="n">
-        <v>2.402135026483953</v>
+        <v>9.749185276887284</v>
       </c>
       <c r="G40" t="n">
-        <v>1.933007051992911</v>
+        <v>9.740501172121165</v>
       </c>
       <c r="H40" t="n">
-        <v>3.35909836127389</v>
+        <v>10.15190180287177</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFIELD_HUNTNGTN</t>
+          <t>mv_f0_lv_SALLYS_RUN_ORMOND</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfield_huntngtn</t>
+          <t>mv_f0_lv_sallys_run_ormond</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>1.918467312805287</v>
+        <v>9.108759250772401</v>
       </c>
       <c r="F41" t="n">
-        <v>1.918942891843919</v>
+        <v>9.111954840386062</v>
       </c>
       <c r="G41" t="n">
-        <v>1.918467312805287</v>
+        <v>9.108759250772401</v>
       </c>
       <c r="H41" t="n">
-        <v>1.961187236213034</v>
+        <v>9.350059737102587</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>mv_f0_lv_THE_PARKWAY_KARKALLA</t>
+          <t>mv_f0_lv_HALLAM_RD_RETIREMENT</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mv_f0_lv_the_parkway_karkalla</t>
+          <t>mv_f0_lv_hallam_rd_retirement</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.756843051015878</v>
+        <v>9.102383111298376</v>
       </c>
       <c r="F42" t="n">
-        <v>2.441051062629912</v>
+        <v>9.107100059082295</v>
       </c>
       <c r="G42" t="n">
-        <v>-1.756843051015878</v>
+        <v>9.102383111298376</v>
       </c>
       <c r="H42" t="n">
-        <v>3.45160934300538</v>
+        <v>9.395458496288052</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_SCHOOL</t>
+          <t>mv_f0_lv_LESLEY_AMY</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_school</t>
+          <t>mv_f0_lv_lesley_amy</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>1.578680583181973</v>
+        <v>8.60194891009167</v>
       </c>
       <c r="F43" t="n">
-        <v>1.594729311459841</v>
+        <v>8.607821631438407</v>
       </c>
       <c r="G43" t="n">
-        <v>1.578680583181973</v>
+        <v>8.60194891009167</v>
       </c>
       <c r="H43" t="n">
-        <v>1.804355555461587</v>
+        <v>8.919861141425528</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LEOPOLD_WENDY</t>
+          <t>mv_f0_lv_ORMOND_SCHOOL</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mv_f0_lv_leopold_wendy</t>
+          <t>mv_f0_lv_ormond_school</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>1.56819091085003</v>
+        <v>6.415646017361465</v>
       </c>
       <c r="F44" t="n">
-        <v>1.576109800787334</v>
+        <v>6.421820722508365</v>
       </c>
       <c r="G44" t="n">
-        <v>1.56819091085003</v>
+        <v>6.415646017361465</v>
       </c>
       <c r="H44" t="n">
-        <v>1.725986256995736</v>
+        <v>6.697190990592787</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SALLYS_RUN_ORMOND</t>
+          <t>mv_f0_lv_SPRINGFIELD_HUNTNGTN</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mv_f0_lv_sallys_run_ormond</t>
+          <t>mv_f0_lv_springfield_huntngtn</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.43671286136442</v>
+        <v>5.02172330012754</v>
       </c>
       <c r="F45" t="n">
-        <v>1.444117217402911</v>
+        <v>5.022054537274149</v>
       </c>
       <c r="G45" t="n">
-        <v>1.43671286136442</v>
+        <v>5.02172330012754</v>
       </c>
       <c r="H45" t="n">
-        <v>1.58276316636098</v>
+        <v>5.079402345820294</v>
       </c>
     </row>
     <row r="46">
@@ -1802,16 +1802,16 @@
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>1.297204486817126</v>
+        <v>1.485352243040447</v>
       </c>
       <c r="F46" t="n">
-        <v>1.403701136360668</v>
+        <v>1.486103433303384</v>
       </c>
       <c r="G46" t="n">
-        <v>-1.297204486817126</v>
+        <v>1.485352243040447</v>
       </c>
       <c r="H46" t="n">
-        <v>1.833522862040041</v>
+        <v>1.5325976509741</v>
       </c>
     </row>
   </sheetData>
@@ -2060,139 +2060,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.284135886578531</v>
+        <v>15.07806935688631</v>
       </c>
       <c r="C2" t="n">
-        <v>3.604668341633563</v>
+        <v>11.8800789544094</v>
       </c>
       <c r="D2" t="n">
-        <v>10.87717908037843</v>
+        <v>21.93905223602511</v>
       </c>
       <c r="E2" t="n">
-        <v>6.115992751759915</v>
+        <v>14.95607109383139</v>
       </c>
       <c r="F2" t="n">
-        <v>1.072540820890488</v>
+        <v>24.81343692019105</v>
       </c>
       <c r="G2" t="n">
-        <v>4.279349909466937</v>
+        <v>16.71039823368699</v>
       </c>
       <c r="H2" t="n">
-        <v>3.027731851177627</v>
+        <v>17.68936650645801</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7608861115942105</v>
+        <v>1.438106835106794</v>
       </c>
       <c r="J2" t="n">
-        <v>1.804355555461587</v>
+        <v>6.697190990592787</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5069157427119322</v>
+        <v>16.40776663526857</v>
       </c>
       <c r="L2" t="n">
-        <v>8.487403622643718</v>
+        <v>20.04931373211755</v>
       </c>
       <c r="M2" t="n">
-        <v>3.932594708758444</v>
+        <v>20.20790339639703</v>
       </c>
       <c r="N2" t="n">
-        <v>2.849301478136582</v>
+        <v>14.7758238950241</v>
       </c>
       <c r="O2" t="n">
-        <v>2.689053749265423</v>
+        <v>10.63898829164378</v>
       </c>
       <c r="P2" t="n">
-        <v>5.520102144718336</v>
+        <v>19.83111396951884</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.0603186085347</v>
+        <v>14.95379024174054</v>
       </c>
       <c r="R2" t="n">
-        <v>3.453112922529666</v>
+        <v>17.62291649051376</v>
       </c>
       <c r="S2" t="n">
-        <v>3.434869713703172</v>
+        <v>17.86412469313048</v>
       </c>
       <c r="T2" t="n">
-        <v>8.806721057119923</v>
+        <v>21.49094986096896</v>
       </c>
       <c r="U2" t="n">
-        <v>3.825432600978033</v>
+        <v>14.35180735365237</v>
       </c>
       <c r="V2" t="n">
-        <v>1.87574738939754</v>
+        <v>4.964044254434786</v>
       </c>
       <c r="W2" t="n">
-        <v>5.446760694749322</v>
+        <v>15.74312680178592</v>
       </c>
       <c r="X2" t="n">
-        <v>1.725986256995736</v>
+        <v>11.26078376328444</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.630383361263199</v>
+        <v>18.78854535464792</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.139401762027056</v>
+        <v>17.25868129511795</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.048871643254067</v>
+        <v>8.809307726308699</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.924463818223714</v>
+        <v>16.02264943159969</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.708628956944892</v>
+        <v>19.10836696335945</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.185246479236966</v>
+        <v>15.12208740062074</v>
       </c>
       <c r="AE2" t="n">
-        <v>6.397113355207807</v>
+        <v>16.51759547192204</v>
       </c>
       <c r="AF2" t="n">
-        <v>4.260786257152596</v>
+        <v>15.97058432683876</v>
       </c>
       <c r="AG2" t="n">
-        <v>5.249957860836187</v>
+        <v>12.27653457129389</v>
       </c>
       <c r="AH2" t="n">
-        <v>-3.45160934300538</v>
+        <v>18.91597116017147</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.321622799797002</v>
+        <v>12.29732212347522</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.539052766063463</v>
+        <v>10.15190180287177</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.29066255636786</v>
+        <v>9.350059737102587</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.554754442757739</v>
+        <v>8.284036678757811</v>
       </c>
       <c r="AM2" t="n">
-        <v>6.213166199657014</v>
+        <v>17.73559584672712</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.673608087326713</v>
+        <v>15.05756921512721</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.535607233510099</v>
+        <v>16.38526148905168</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.085041109006529</v>
+        <v>10.44498606567276</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.131211298030582</v>
+        <v>15.08794480290338</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.149538314906152</v>
+        <v>18.68527777588395</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.755815650100864</v>
+        <v>22.09372264574459</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.523401511373297</v>
+        <v>12.78489466801624</v>
       </c>
     </row>
     <row r="3">
@@ -2200,139 +2200,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4.785749591300761</v>
+        <v>14.66966806836041</v>
       </c>
       <c r="C3" t="n">
-        <v>4.301027796829302</v>
+        <v>9.881324912847749</v>
       </c>
       <c r="D3" t="n">
-        <v>9.800230809176639</v>
+        <v>20.67133450524295</v>
       </c>
       <c r="E3" t="n">
-        <v>4.552437269091552</v>
+        <v>13.97405571157345</v>
       </c>
       <c r="F3" t="n">
-        <v>6.537161873601619</v>
+        <v>20.957763493935</v>
       </c>
       <c r="G3" t="n">
-        <v>5.820749377119498</v>
+        <v>17.20503641658092</v>
       </c>
       <c r="H3" t="n">
-        <v>2.550046605690355</v>
+        <v>18.37063528893662</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.833522862040041</v>
+        <v>1.5325976509741</v>
       </c>
       <c r="J3" t="n">
-        <v>1.353005610902359</v>
+        <v>6.134101044130142</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35909836127389</v>
+        <v>16.31918675138066</v>
       </c>
       <c r="L3" t="n">
-        <v>8.644811506173951</v>
+        <v>19.36687092269202</v>
       </c>
       <c r="M3" t="n">
-        <v>4.668319414375205</v>
+        <v>19.9087210634161</v>
       </c>
       <c r="N3" t="n">
-        <v>5.208288876290855</v>
+        <v>14.6683635438186</v>
       </c>
       <c r="O3" t="n">
-        <v>3.847275406962876</v>
+        <v>11.38493707714738</v>
       </c>
       <c r="P3" t="n">
-        <v>5.074670935663299</v>
+        <v>22.71230479728805</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.061202773697545</v>
+        <v>16.78124748820939</v>
       </c>
       <c r="R3" t="n">
-        <v>2.889513450052608</v>
+        <v>15.99777145287985</v>
       </c>
       <c r="S3" t="n">
-        <v>5.123316913352873</v>
+        <v>16.55058698396441</v>
       </c>
       <c r="T3" t="n">
-        <v>6.475945397805141</v>
+        <v>20.91160786757982</v>
       </c>
       <c r="U3" t="n">
-        <v>7.290221048335489</v>
+        <v>10.9584689646352</v>
       </c>
       <c r="V3" t="n">
-        <v>1.961187236213034</v>
+        <v>5.079402345820294</v>
       </c>
       <c r="W3" t="n">
-        <v>4.618991866447562</v>
+        <v>14.65388207626278</v>
       </c>
       <c r="X3" t="n">
-        <v>1.410395564704324</v>
+        <v>11.99701106241501</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.402810891630764</v>
+        <v>18.85454770446196</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.018027849962408</v>
+        <v>14.50251117764969</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.681220320479888</v>
+        <v>9.395458496288052</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.137086436121692</v>
+        <v>13.8606998072146</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.777218044954516</v>
+        <v>16.64813133984202</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.611112909382374</v>
+        <v>14.01267001301277</v>
       </c>
       <c r="AE3" t="n">
-        <v>5.800318494405289</v>
+        <v>18.12061637209431</v>
       </c>
       <c r="AF3" t="n">
-        <v>6.023638720970769</v>
+        <v>14.9660749514917</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.592144626623679</v>
+        <v>13.0313326060332</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.06207675902637533</v>
+        <v>19.33240797705709</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.369746231681653</v>
+        <v>14.84501400289153</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.547245109952858</v>
+        <v>9.329100541370561</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.58276316636098</v>
+        <v>8.867458764442215</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.942785935573241</v>
+        <v>8.919861141425528</v>
       </c>
       <c r="AM3" t="n">
-        <v>6.127938363758965</v>
+        <v>17.21627848096804</v>
       </c>
       <c r="AN3" t="n">
-        <v>5.606788892959372</v>
+        <v>13.07395706029272</v>
       </c>
       <c r="AO3" t="n">
-        <v>3.047895953626558</v>
+        <v>17.43624095525147</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.889903350395919</v>
+        <v>9.791163996665368</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.27609853201178</v>
+        <v>16.24184527187982</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.40637461651523</v>
+        <v>16.8511489997417</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.568473645623165</v>
+        <v>20.6836532938557</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.511091451548868</v>
+        <v>13.46801063219757</v>
       </c>
     </row>
   </sheetData>

--- a/nando/Nando_final/metrics/net_3_Urban_HPK11/trafo_loading_compare.xlsx
+++ b/nando/Nando_final/metrics/net_3_Urban_HPK11/trafo_loading_compare.xlsx
@@ -482,1336 +482,1336 @@
         <v>88</v>
       </c>
       <c r="E2" t="n">
-        <v>14.87386871262336</v>
+        <v>1.468137670637788</v>
       </c>
       <c r="F2" t="n">
-        <v>14.89142818982848</v>
+        <v>1.534247713717829</v>
       </c>
       <c r="G2" t="n">
-        <v>14.87386871262336</v>
+        <v>-1.126748772639983</v>
       </c>
       <c r="H2" t="n">
-        <v>24.81343692019105</v>
+        <v>11.09870174680956</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mv_f0_lv_KERSHAW_ORMOND</t>
+          <t>mv_f0_lv_P12_SCHOOL_ORMOND</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mv_f0_lv_kershaw_ormond</t>
+          <t>mv_f0_lv_p12_school_ormond</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>22.88560020706302</v>
+        <v>11.08188464259903</v>
       </c>
       <c r="F3" t="n">
-        <v>22.96665520335966</v>
+        <v>11.08189740283071</v>
       </c>
       <c r="G3" t="n">
-        <v>22.88560020706302</v>
+        <v>-11.08188464259903</v>
       </c>
       <c r="H3" t="n">
-        <v>24.81343692019105</v>
+        <v>11.09870174680956</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TANGERINE_NORWEGIAN</t>
+          <t>mv_f0_lv_KERSHAW_ORMOND</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mv_f0_lv_tangerine_norwegian</t>
+          <t>mv_f0_lv_kershaw_ormond</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>21.38868796980015</v>
+        <v>5.792913450897565</v>
       </c>
       <c r="F4" t="n">
-        <v>21.4003048334307</v>
+        <v>5.803396923923547</v>
       </c>
       <c r="G4" t="n">
-        <v>21.38868796980015</v>
+        <v>-5.792913450897565</v>
       </c>
       <c r="H4" t="n">
-        <v>22.09372264574459</v>
+        <v>6.141581784726942</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mv_f0_lv_CHATSWOOD_FLEET</t>
+          <t>mv_f0_lv_SPRINGFIELD_JANET</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mv_f0_lv_chatswood_fleet</t>
+          <t>mv_f0_lv_springfield_janet</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>21.30519337063403</v>
+        <v>3.536260802381791</v>
       </c>
       <c r="F5" t="n">
-        <v>21.31462037244255</v>
+        <v>3.536289961288313</v>
       </c>
       <c r="G5" t="n">
-        <v>21.30519337063403</v>
+        <v>-3.536260802381791</v>
       </c>
       <c r="H5" t="n">
-        <v>21.93905223602511</v>
+        <v>3.550621437694598</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GOLDEN_CHERRYWOOD</t>
+          <t>mv_f0_lv_THE_PARKWAY_KARKALLA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mv_f0_lv_golden_cherrywood</t>
+          <t>mv_f0_lv_the_parkway_karkalla</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>21.27170938340344</v>
+        <v>3.345345268537971</v>
       </c>
       <c r="F6" t="n">
-        <v>21.3204346869026</v>
+        <v>3.354905193844571</v>
       </c>
       <c r="G6" t="n">
-        <v>21.27170938340344</v>
+        <v>-3.345345268537971</v>
       </c>
       <c r="H6" t="n">
-        <v>22.71230479728805</v>
+        <v>3.598433976219468</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mv_f0_lv_MEREDITH_HARVEY</t>
+          <t>mv_f0_lv_TANGERINE_NORWEGIAN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mv_f0_lv_meredith_harvey</t>
+          <t>mv_f0_lv_tangerine_norwegian</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>21.20127886427439</v>
+        <v>3.098878930656117</v>
       </c>
       <c r="F7" t="n">
-        <v>21.20325764516043</v>
+        <v>3.128552405236609</v>
       </c>
       <c r="G7" t="n">
-        <v>21.20127886427439</v>
+        <v>-3.098878930656117</v>
       </c>
       <c r="H7" t="n">
-        <v>21.49094986096896</v>
+        <v>3.528750452680285</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HALLAM_EDEYS</t>
+          <t>mv_f0_lv_CHISHOLM_KERSHAW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hallam_edeys</t>
+          <t>mv_f0_lv_chisholm_kershaw</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>20.05831222990656</v>
+        <v>2.191775972269111</v>
       </c>
       <c r="F8" t="n">
-        <v>20.05887003371603</v>
+        <v>2.194257123646928</v>
       </c>
       <c r="G8" t="n">
-        <v>20.05831222990656</v>
+        <v>-2.191775972269111</v>
       </c>
       <c r="H8" t="n">
-        <v>20.20790339639703</v>
+        <v>2.29609477239201</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TUILERIES_PROVENCE</t>
+          <t>mv_f0_lv_EDEYS_PIONEER</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mv_f0_lv_tuileries_provence</t>
+          <t>mv_f0_lv_edeys_pioneer</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>19.70809232740478</v>
+        <v>2.119683563006067</v>
       </c>
       <c r="F9" t="n">
-        <v>19.71104602076068</v>
+        <v>2.136235587449035</v>
       </c>
       <c r="G9" t="n">
-        <v>19.70809232740478</v>
+        <v>-2.119683563006067</v>
       </c>
       <c r="H9" t="n">
-        <v>20.04931373211755</v>
+        <v>2.385096595477405</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mv_f0_lv_THE_PARKWAY_KARKALLA</t>
+          <t>mv_f0_lv_NORWEGIAN_GLASSCOCKS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mv_f0_lv_the_parkway_karkalla</t>
+          <t>mv_f0_lv_norwegian_glasscocks</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>19.12418956861428</v>
+        <v>1.882395810907788</v>
       </c>
       <c r="F10" t="n">
-        <v>19.12532304464188</v>
+        <v>1.887487509761329</v>
       </c>
       <c r="G10" t="n">
-        <v>19.12418956861428</v>
+        <v>-1.882395810907788</v>
       </c>
       <c r="H10" t="n">
-        <v>19.33240797705709</v>
+        <v>2.020942231221834</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mv_f0_lv_NORWEGIAN_GLASSCOCKS</t>
+          <t>mv_f0_lv_ORMOND_TANGERINE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mv_f0_lv_norwegian_glasscocks</t>
+          <t>mv_f0_lv_ormond_tangerine</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>18.82154652955494</v>
+        <v>1.752420186734663</v>
       </c>
       <c r="F11" t="n">
-        <v>18.82157546120268</v>
+        <v>1.752442227359164</v>
       </c>
       <c r="G11" t="n">
-        <v>18.82154652955494</v>
+        <v>-1.752420186734663</v>
       </c>
       <c r="H11" t="n">
-        <v>18.85454770446196</v>
+        <v>1.761209348036886</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mv_f0_lv_CHISHOLM_KERSHAW</t>
+          <t>mv_f0_lv_MALABAR_BYRON</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mv_f0_lv_chisholm_kershaw</t>
+          <t>mv_f0_lv_malabar_byron</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>18.03000089769731</v>
+        <v>1.638749436465869</v>
       </c>
       <c r="F12" t="n">
-        <v>18.03321835279163</v>
+        <v>1.732562501597151</v>
       </c>
       <c r="G12" t="n">
-        <v>18.03000089769731</v>
+        <v>-1.638749436465869</v>
       </c>
       <c r="H12" t="n">
-        <v>18.37063528893662</v>
+        <v>2.20113107416697</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mv_f0_lv_CORAL_CLAUD</t>
+          <t>mv_f0_lv_GERALDINE_PAULINE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mv_f0_lv_coral_claud</t>
+          <t>mv_f0_lv_geraldine_pauline</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>17.87824915160074</v>
+        <v>1.623105634232378</v>
       </c>
       <c r="F13" t="n">
-        <v>17.92051847903733</v>
+        <v>1.623439627748742</v>
       </c>
       <c r="G13" t="n">
-        <v>17.87824915160074</v>
+        <v>-1.623105634232378</v>
       </c>
       <c r="H13" t="n">
-        <v>19.10836696335945</v>
+        <v>1.656034725748638</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mv_f0_lv_PARKWAY_REDWOOD</t>
+          <t>mv_f0_lv_JESSICA_GERALDINE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mv_f0_lv_parkway_redwood</t>
+          <t>mv_f0_lv_jessica_geraldine</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>17.76821338781283</v>
+        <v>1.518110197284749</v>
       </c>
       <c r="F14" t="n">
-        <v>17.79186370470276</v>
+        <v>1.905053472428609</v>
       </c>
       <c r="G14" t="n">
-        <v>17.76821338781283</v>
+        <v>-1.518110197284749</v>
       </c>
       <c r="H14" t="n">
-        <v>18.68527777588395</v>
+        <v>2.66900991564094</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TOOMAH_STRATHARD</t>
+          <t>mv_f0_lv_TUILERIES_PROVENCE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mv_f0_lv_toomah_strathard</t>
+          <t>mv_f0_lv_tuileries_provence</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>17.47593716384758</v>
+        <v>1.493333059476441</v>
       </c>
       <c r="F15" t="n">
-        <v>17.47786607072911</v>
+        <v>1.664658348330728</v>
       </c>
       <c r="G15" t="n">
-        <v>17.47593716384758</v>
+        <v>-1.493333059476441</v>
       </c>
       <c r="H15" t="n">
-        <v>17.73559584672712</v>
+        <v>2.228889848678961</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LEOPOLD_HAZEL</t>
+          <t>mv_f0_lv_HALLAM_EDEYS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mv_f0_lv_leopold_hazel</t>
+          <t>mv_f0_lv_hallam_edeys</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>17.31910592200818</v>
+        <v>1.465029535425548</v>
       </c>
       <c r="F16" t="n">
-        <v>17.33764254272581</v>
+        <v>1.557026272870172</v>
       </c>
       <c r="G16" t="n">
-        <v>17.31910592200818</v>
+        <v>-1.465029535425548</v>
       </c>
       <c r="H16" t="n">
-        <v>18.12061637209431</v>
+        <v>1.992304866480191</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFLD_KATHERINE</t>
+          <t>mv_f0_lv_GOLDEN_CHERRYWOOD</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfld_katherine</t>
+          <t>mv_f0_lv_golden_cherrywood</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>17.20735583854744</v>
+        <v>1.44397144984069</v>
       </c>
       <c r="F17" t="n">
-        <v>17.2198850252475</v>
+        <v>1.451406164314974</v>
       </c>
       <c r="G17" t="n">
-        <v>17.20735583854744</v>
+        <v>-1.44397144984069</v>
       </c>
       <c r="H17" t="n">
-        <v>17.86412469313048</v>
+        <v>1.590689907631386</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mv_f0_lv_MALABAR_BYRON</t>
+          <t>mv_f0_lv_TIMMS_STRATHAIRD</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mv_f0_lv_malabar_byron</t>
+          <t>mv_f0_lv_timms_strathaird</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>16.95771732513396</v>
+        <v>1.36968168910583</v>
       </c>
       <c r="F18" t="n">
-        <v>16.95952073651088</v>
+        <v>1.484676257630417</v>
       </c>
       <c r="G18" t="n">
-        <v>16.95771732513396</v>
+        <v>-1.36968168910583</v>
       </c>
       <c r="H18" t="n">
-        <v>17.20503641658092</v>
+        <v>1.942600235235783</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mv_f0_lv_EDEYS_MOLLISONS</t>
+          <t>mv_f0_lv_SPRINGFLD_KATHERINE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mv_f0_lv_edeys_mollisons</t>
+          <t>mv_f0_lv_springfld_katherine</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>16.91075122215157</v>
+        <v>1.333456202048635</v>
       </c>
       <c r="F19" t="n">
-        <v>16.91891386458051</v>
+        <v>1.426937610682876</v>
       </c>
       <c r="G19" t="n">
-        <v>16.91075122215157</v>
+        <v>-1.333456202048635</v>
       </c>
       <c r="H19" t="n">
-        <v>17.43624095525147</v>
+        <v>1.841437995028841</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mv_f0_lv_COMMUNITY_HARRINGTON</t>
+          <t>mv_f0_lv_NIMBUS_AMBER</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mv_f0_lv_community_harrington</t>
+          <t>mv_f0_lv_nimbus_amber</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>16.81034397169681</v>
+        <v>1.306278468483355</v>
       </c>
       <c r="F20" t="n">
-        <v>16.82997143625323</v>
+        <v>1.48180732452899</v>
       </c>
       <c r="G20" t="n">
-        <v>16.81034397169681</v>
+        <v>-0.6995637996670085</v>
       </c>
       <c r="H20" t="n">
-        <v>17.62291649051376</v>
+        <v>2.005842268150364</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mv_f0_lv_BARINGA_PARK_CASPIAN</t>
+          <t>mv_f0_lv_HIGHMOUNT_ORMOND</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mv_f0_lv_baringa_park_caspian</t>
+          <t>mv_f0_lv_highmount_ormond</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>16.36347669332461</v>
+        <v>1.240074658378082</v>
       </c>
       <c r="F21" t="n">
-        <v>16.36353663154562</v>
+        <v>1.256471083104572</v>
       </c>
       <c r="G21" t="n">
-        <v>16.36347669332461</v>
+        <v>0.2023225749303856</v>
       </c>
       <c r="H21" t="n">
-        <v>16.40776663526857</v>
+        <v>1.442397233308467</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mv_f0_lv_VON_NIDA_DULWICH</t>
+          <t>mv_f0_lv_ORMOND_STRATHAIRD</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mv_f0_lv_von_nida_dulwich</t>
+          <t>mv_f0_lv_ormond_strathaird</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>15.88059623638382</v>
+        <v>1.200104978674156</v>
       </c>
       <c r="F22" t="n">
-        <v>15.94027776584066</v>
+        <v>1.206235112312153</v>
       </c>
       <c r="G22" t="n">
-        <v>15.88059623638382</v>
+        <v>-1.200104978674156</v>
       </c>
       <c r="H22" t="n">
-        <v>17.25868129511795</v>
+        <v>1.321559440659771</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mv_f0_lv_EDEYS_PIONEER</t>
+          <t>mv_f0_lv_CORAL_CLAUD</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mv_f0_lv_edeys_pioneer</t>
+          <t>mv_f0_lv_coral_claud</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>15.86751886497496</v>
+        <v>1.160532042628059</v>
       </c>
       <c r="F23" t="n">
-        <v>15.89380555207765</v>
+        <v>1.270308387261093</v>
       </c>
       <c r="G23" t="n">
-        <v>15.86751886497496</v>
+        <v>0.5165740767590101</v>
       </c>
       <c r="H23" t="n">
-        <v>16.78124748820939</v>
+        <v>1.677106119387069</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HIGHMOUNT_ORMOND</t>
+          <t>mv_f0_lv_SPRINGFIELD_HUNTNGTN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mv_f0_lv_highmount_ormond</t>
+          <t>mv_f0_lv_springfield_huntngtn</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>15.6648950373916</v>
+        <v>1.120113799068521</v>
       </c>
       <c r="F24" t="n">
-        <v>15.67551619901469</v>
+        <v>1.284883784921923</v>
       </c>
       <c r="G24" t="n">
-        <v>15.6648950373916</v>
+        <v>1.120113799068521</v>
       </c>
       <c r="H24" t="n">
-        <v>16.24184527187982</v>
+        <v>1.749614726702127</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mv_f0_lv_NIMBUS_AMBER</t>
+          <t>mv_f0_lv_COMMUNITY_HARRINGTON</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mv_f0_lv_nimbus_amber</t>
+          <t>mv_f0_lv_community_harrington</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>15.46832963916523</v>
+        <v>0.9716109407358822</v>
       </c>
       <c r="F25" t="n">
-        <v>15.47648156388161</v>
+        <v>1.065342952901249</v>
       </c>
       <c r="G25" t="n">
-        <v>15.46832963916523</v>
+        <v>-0.9716109407358822</v>
       </c>
       <c r="H25" t="n">
-        <v>15.97058432683876</v>
+        <v>1.408563783887963</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mv_f0_lv_RALEIGH_LOWDEN</t>
+          <t>mv_f0_lv_SHERWOOD_FLEET</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mv_f0_lv_raleigh_lowden</t>
+          <t>mv_f0_lv_sherwood_fleet</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>15.19850443902435</v>
+        <v>0.9560257118424031</v>
       </c>
       <c r="F26" t="n">
-        <v>15.2082592922748</v>
+        <v>1.331257962119055</v>
       </c>
       <c r="G26" t="n">
-        <v>15.19850443902435</v>
+        <v>-0.9264246326612904</v>
       </c>
       <c r="H26" t="n">
-        <v>15.74312680178592</v>
+        <v>1.882450344503694</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mv_f0_lv_TIMMS_STRATHAIRD</t>
+          <t>mv_f0_lv_EDEYS_MOLLISONS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mv_f0_lv_timms_strathaird</t>
+          <t>mv_f0_lv_edeys_mollisons</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>14.94167461940715</v>
+        <v>0.9491265176005514</v>
       </c>
       <c r="F27" t="n">
-        <v>14.98072584946505</v>
+        <v>0.9496471736285989</v>
       </c>
       <c r="G27" t="n">
-        <v>14.94167461940715</v>
+        <v>0.9491265176005514</v>
       </c>
       <c r="H27" t="n">
-        <v>16.02264943159969</v>
+        <v>0.9805686544273691</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_STRATHAIRD</t>
+          <t>mv_f0_lv_CHATSWOOD_FLEET</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_strathaird</t>
+          <t>mv_f0_lv_chatswood_fleet</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>14.72209371942135</v>
+        <v>0.8543430674759556</v>
       </c>
       <c r="F28" t="n">
-        <v>14.72219176669004</v>
+        <v>0.8968294234319212</v>
       </c>
       <c r="G28" t="n">
-        <v>14.72209371942135</v>
+        <v>-0.2727653529849547</v>
       </c>
       <c r="H28" t="n">
-        <v>14.7758238950241</v>
+        <v>1.12710842046091</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mv_f0_lv_MICHELLE_SIMON</t>
+          <t>mv_f0_lv_PARKWAY_REDWOOD</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mv_f0_lv_michelle_simon</t>
+          <t>mv_f0_lv_parkway_redwood</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>14.56737870681676</v>
+        <v>0.7736462159562656</v>
       </c>
       <c r="F29" t="n">
-        <v>14.57793620931303</v>
+        <v>0.8996163514640025</v>
       </c>
       <c r="G29" t="n">
-        <v>14.56737870681676</v>
+        <v>-0.7736462159562656</v>
       </c>
       <c r="H29" t="n">
-        <v>15.12208740062074</v>
+        <v>1.232755257860207</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GREENVIEW_SNOWDONIA</t>
+          <t>mv_f0_lv_TOOMAH_STRATHARD</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mv_f0_lv_greenview_snowdonia</t>
+          <t>mv_f0_lv_toomah_strathard</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>14.46506340270242</v>
+        <v>0.7106046722609873</v>
       </c>
       <c r="F30" t="n">
-        <v>14.47339448080334</v>
+        <v>0.7754123795778107</v>
       </c>
       <c r="G30" t="n">
-        <v>14.46506340270242</v>
+        <v>0.3103310460836584</v>
       </c>
       <c r="H30" t="n">
-        <v>14.95607109383139</v>
+        <v>1.020935718344646</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mv_f0_lv_JESSICA_GERALDINE</t>
+          <t>mv_f0_lv_MEREDITH_HARVEY</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mv_f0_lv_jessica_geraldine</t>
+          <t>mv_f0_lv_meredith_harvey</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>14.06576313770996</v>
+        <v>0.6575036235384637</v>
       </c>
       <c r="F31" t="n">
-        <v>14.1006869315421</v>
+        <v>0.6575162775645296</v>
       </c>
       <c r="G31" t="n">
-        <v>14.06576313770996</v>
+        <v>-0.6575036235384637</v>
       </c>
       <c r="H31" t="n">
-        <v>15.05756921512721</v>
+        <v>0.6615828754436208</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LESLEY_CARMEN</t>
+          <t>mv_f0_lv_RALEIGH_LOWDEN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mv_f0_lv_lesley_carmen</t>
+          <t>mv_f0_lv_raleigh_lowden</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>13.57116806318338</v>
+        <v>0.6066553328084137</v>
       </c>
       <c r="F32" t="n">
-        <v>13.63082118132578</v>
+        <v>0.6581335434007319</v>
       </c>
       <c r="G32" t="n">
-        <v>13.57116806318338</v>
+        <v>0.2551647862153317</v>
       </c>
       <c r="H32" t="n">
-        <v>14.84501400289153</v>
+        <v>0.8618201190237453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HADLEY_CHESTERFIELD</t>
+          <t>mv_f0_lv_BARINGA_PARK_CASPIAN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hadley_chesterfield</t>
+          <t>mv_f0_lv_baringa_park_caspian</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>13.1264526501069</v>
+        <v>0.5965633971604376</v>
       </c>
       <c r="F33" t="n">
-        <v>13.1308956674946</v>
+        <v>0.6725428763956607</v>
       </c>
       <c r="G33" t="n">
-        <v>13.1264526501069</v>
+        <v>-0.310525415640889</v>
       </c>
       <c r="H33" t="n">
-        <v>13.46801063219757</v>
+        <v>0.9070888128013266</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFIELD_JANET</t>
+          <t>mv_f0_lv_VIEWSIDE_NEESAN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfield_janet</t>
+          <t>mv_f0_lv_viewside_neesan</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>12.65513815914379</v>
+        <v>0.5467865634572053</v>
       </c>
       <c r="F34" t="n">
-        <v>12.76836748306578</v>
+        <v>0.6377005944162396</v>
       </c>
       <c r="G34" t="n">
-        <v>12.65513815914379</v>
+        <v>-0.5467865634572053</v>
       </c>
       <c r="H34" t="n">
-        <v>14.35180735365237</v>
+        <v>0.8749427795212696</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mv_f0_lv_GERALDINE_PAULINE</t>
+          <t>mv_f0_lv_LEOPOLD_WENDY</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mv_f0_lv_geraldine_pauline</t>
+          <t>mv_f0_lv_leopold_wendy</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>12.65393358866355</v>
+        <v>0.4905086712083491</v>
       </c>
       <c r="F35" t="n">
-        <v>12.65956023267077</v>
+        <v>0.5020909519423081</v>
       </c>
       <c r="G35" t="n">
-        <v>12.65393358866355</v>
+        <v>0.4905086712083491</v>
       </c>
       <c r="H35" t="n">
-        <v>13.0313326060332</v>
+        <v>0.5977307188093572</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LEOPOLD_WENDY</t>
+          <t>mv_f0_lv_HALLAM_RD_RETIREMENT</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mv_f0_lv_leopold_wendy</t>
+          <t>mv_f0_lv_hallam_rd_retirement</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>11.62889741284973</v>
+        <v>0.4714781140425406</v>
       </c>
       <c r="F36" t="n">
-        <v>11.63472228708444</v>
+        <v>0.4861250730410852</v>
       </c>
       <c r="G36" t="n">
-        <v>11.62889741284973</v>
+        <v>0.4714781140425406</v>
       </c>
       <c r="H36" t="n">
-        <v>11.99701106241501</v>
+        <v>0.5899094216351255</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SHERWOOD_FLEET</t>
+          <t>mv_f0_lv_SALLYS_RUN_ORMOND</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mv_f0_lv_sherwood_fleet</t>
+          <t>mv_f0_lv_sallys_run_ormond</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>11.01196268439558</v>
+        <v>0.4613307684349519</v>
       </c>
       <c r="F37" t="n">
-        <v>11.01827718203573</v>
+        <v>0.6051067750302427</v>
       </c>
       <c r="G37" t="n">
-        <v>11.01196268439558</v>
+        <v>-0.3915713616733449</v>
       </c>
       <c r="H37" t="n">
-        <v>11.38493707714738</v>
+        <v>0.8529021301082969</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>mv_f0_lv_OAKGROVE_OXENFORD</t>
+          <t>mv_f0_lv_HADLEY_CHESTERFIELD</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>mv_f0_lv_oakgrove_oxenford</t>
+          <t>mv_f0_lv_hadley_chesterfield</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>10.88070193362858</v>
+        <v>0.4277664840072077</v>
       </c>
       <c r="F38" t="n">
-        <v>10.92650122400274</v>
+        <v>0.5995120848606067</v>
       </c>
       <c r="G38" t="n">
-        <v>10.88070193362858</v>
+        <v>0.4277664840072077</v>
       </c>
       <c r="H38" t="n">
-        <v>11.8800789544094</v>
+        <v>0.8478028813039451</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_TANGERINE</t>
+          <t>mv_f0_lv_OAKGROVE_OXENFORD</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_tangerine</t>
+          <t>mv_f0_lv_oakgrove_oxenford</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>10.11807503116906</v>
+        <v>0.4197263300752363</v>
       </c>
       <c r="F39" t="n">
-        <v>10.12335483724872</v>
+        <v>0.4403906084695607</v>
       </c>
       <c r="G39" t="n">
-        <v>10.11807503116906</v>
+        <v>-0.4197263300752363</v>
       </c>
       <c r="H39" t="n">
-        <v>10.44498606567276</v>
+        <v>0.553044355374757</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mv_f0_lv_VIEWSIDE_NEESAN</t>
+          <t>mv_f0_lv_VON_NIDA_DULWICH</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mv_f0_lv_viewside_neesan</t>
+          <t>mv_f0_lv_von_nida_dulwich</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>9.740501172121165</v>
+        <v>0.4020849071235979</v>
       </c>
       <c r="F40" t="n">
-        <v>9.749185276887284</v>
+        <v>0.4453240694007893</v>
       </c>
       <c r="G40" t="n">
-        <v>9.740501172121165</v>
+        <v>-0.4020849071235979</v>
       </c>
       <c r="H40" t="n">
-        <v>10.15190180287177</v>
+        <v>0.5935039611675634</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SALLYS_RUN_ORMOND</t>
+          <t>mv_f0_lv_MICHELLE_SIMON</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mv_f0_lv_sallys_run_ormond</t>
+          <t>mv_f0_lv_michelle_simon</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>9.108759250772401</v>
+        <v>0.3086254746136783</v>
       </c>
       <c r="F41" t="n">
-        <v>9.111954840386062</v>
+        <v>0.3142279672085497</v>
       </c>
       <c r="G41" t="n">
-        <v>9.108759250772401</v>
+        <v>-0.05907225910272285</v>
       </c>
       <c r="H41" t="n">
-        <v>9.350059737102587</v>
+        <v>0.3676977337164011</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>mv_f0_lv_HALLAM_RD_RETIREMENT</t>
+          <t>mv_f0_lv_LESLEY_AMY</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mv_f0_lv_hallam_rd_retirement</t>
+          <t>mv_f0_lv_lesley_amy</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>9.102383111298376</v>
+        <v>0.2941623566507894</v>
       </c>
       <c r="F42" t="n">
-        <v>9.107100059082295</v>
+        <v>0.3098883247291792</v>
       </c>
       <c r="G42" t="n">
-        <v>9.102383111298376</v>
+        <v>-0.2941623566507894</v>
       </c>
       <c r="H42" t="n">
-        <v>9.395458496288052</v>
+        <v>0.3916266153978345</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>mv_f0_lv_LESLEY_AMY</t>
+          <t>mv_f0_lv_ORMOND_SCHOOL</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mv_f0_lv_lesley_amy</t>
+          <t>mv_f0_lv_ormond_school</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>8.60194891009167</v>
+        <v>0.268493587133344</v>
       </c>
       <c r="F43" t="n">
-        <v>8.607821631438407</v>
+        <v>0.2736400859048073</v>
       </c>
       <c r="G43" t="n">
-        <v>8.60194891009167</v>
+        <v>0.268493587133344</v>
       </c>
       <c r="H43" t="n">
-        <v>8.919861141425528</v>
+        <v>0.321314892326038</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ORMOND_SCHOOL</t>
+          <t>mv_f0_lv_GREENVIEW_SNOWDONIA</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mv_f0_lv_ormond_school</t>
+          <t>mv_f0_lv_greenview_snowdonia</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>6.415646017361465</v>
+        <v>0.2648707642089452</v>
       </c>
       <c r="F44" t="n">
-        <v>6.421820722508365</v>
+        <v>0.300544869126814</v>
       </c>
       <c r="G44" t="n">
-        <v>6.415646017361465</v>
+        <v>-0.2648707642089452</v>
       </c>
       <c r="H44" t="n">
-        <v>6.697190990592787</v>
+        <v>0.4068943419199123</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mv_f0_lv_SPRINGFIELD_HUNTNGTN</t>
+          <t>mv_f0_lv_LESLEY_CARMEN</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mv_f0_lv_springfield_huntngtn</t>
+          <t>mv_f0_lv_lesley_carmen</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5.02172330012754</v>
+        <v>0.2436718607075576</v>
       </c>
       <c r="F45" t="n">
-        <v>5.022054537274149</v>
+        <v>0.2565361436305571</v>
       </c>
       <c r="G45" t="n">
-        <v>5.02172330012754</v>
+        <v>0.0802173128953747</v>
       </c>
       <c r="H45" t="n">
-        <v>5.079402345820294</v>
+        <v>0.3238891736029323</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>mv_f0_lv_P12_SCHOOL_ORMOND</t>
+          <t>mv_f0_lv_LEOPOLD_HAZEL</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mv_f0_lv_p12_school_ormond</t>
+          <t>mv_f0_lv_leopold_hazel</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>1.485352243040447</v>
+        <v>0.2083723679174865</v>
       </c>
       <c r="F46" t="n">
-        <v>1.486103433303384</v>
+        <v>0.2085826322675894</v>
       </c>
       <c r="G46" t="n">
-        <v>1.485352243040447</v>
+        <v>0.2083723679174865</v>
       </c>
       <c r="H46" t="n">
-        <v>1.5325976509741</v>
+        <v>0.2177356350895838</v>
       </c>
     </row>
   </sheetData>
@@ -2060,139 +2060,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>15.07806935688631</v>
+        <v>-0.8695459624775772</v>
       </c>
       <c r="C2" t="n">
-        <v>11.8800789544094</v>
+        <v>-0.2864083047757155</v>
       </c>
       <c r="D2" t="n">
-        <v>21.93905223602511</v>
+        <v>0.5815777144910008</v>
       </c>
       <c r="E2" t="n">
-        <v>14.95607109383139</v>
+        <v>-0.4068943419199123</v>
       </c>
       <c r="F2" t="n">
-        <v>24.81343692019105</v>
+        <v>-5.444245117068188</v>
       </c>
       <c r="G2" t="n">
-        <v>16.71039823368699</v>
+        <v>-1.076367798764769</v>
       </c>
       <c r="H2" t="n">
-        <v>17.68936650645801</v>
+        <v>-2.087457172146213</v>
       </c>
       <c r="I2" t="n">
-        <v>1.438106835106794</v>
+        <v>-11.09870174680956</v>
       </c>
       <c r="J2" t="n">
-        <v>6.697190990592787</v>
+        <v>0.21567228194065</v>
       </c>
       <c r="K2" t="n">
-        <v>16.40776663526857</v>
+        <v>-0.9070888128013266</v>
       </c>
       <c r="L2" t="n">
-        <v>20.04931373211755</v>
+        <v>-0.7577762702739221</v>
       </c>
       <c r="M2" t="n">
-        <v>20.20790339639703</v>
+        <v>-1.992304866480191</v>
       </c>
       <c r="N2" t="n">
-        <v>14.7758238950241</v>
+        <v>-1.078650516688542</v>
       </c>
       <c r="O2" t="n">
-        <v>10.63898829164378</v>
+        <v>0.02960107918111277</v>
       </c>
       <c r="P2" t="n">
-        <v>19.83111396951884</v>
+        <v>-1.590689907631386</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.95379024174054</v>
+        <v>-2.385096595477405</v>
       </c>
       <c r="R2" t="n">
-        <v>17.62291649051376</v>
+        <v>-0.5346580975838009</v>
       </c>
       <c r="S2" t="n">
-        <v>17.86412469313048</v>
+        <v>-0.8254744090684287</v>
       </c>
       <c r="T2" t="n">
-        <v>21.49094986096896</v>
+        <v>-0.6534243716333066</v>
       </c>
       <c r="U2" t="n">
-        <v>14.35180735365237</v>
+        <v>-3.521900167068983</v>
       </c>
       <c r="V2" t="n">
-        <v>4.964044254434786</v>
+        <v>1.749614726702127</v>
       </c>
       <c r="W2" t="n">
-        <v>15.74312680178592</v>
+        <v>0.8618201190237453</v>
       </c>
       <c r="X2" t="n">
-        <v>11.26078376328444</v>
+        <v>0.5977307188093572</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.78854535464792</v>
+        <v>-2.020942231221834</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.25868129511795</v>
+        <v>-0.2106658530796324</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.809307726308699</v>
+        <v>0.3530468064499557</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.02264943159969</v>
+        <v>-0.7967631429758768</v>
       </c>
       <c r="AC2" t="n">
-        <v>19.10836696335945</v>
+        <v>1.677106119387069</v>
       </c>
       <c r="AD2" t="n">
-        <v>15.12208740062074</v>
+        <v>-0.3676977337164011</v>
       </c>
       <c r="AE2" t="n">
-        <v>16.51759547192204</v>
+        <v>0.1990091007453891</v>
       </c>
       <c r="AF2" t="n">
-        <v>15.97058432683876</v>
+        <v>0.6067146688163465</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.27653457129389</v>
+        <v>-1.656034725748638</v>
       </c>
       <c r="AH2" t="n">
-        <v>18.91597116017147</v>
+        <v>-3.092256560856473</v>
       </c>
       <c r="AI2" t="n">
-        <v>12.29732212347522</v>
+        <v>0.3238891736029323</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10.15190180287177</v>
+        <v>-0.8749427795212696</v>
       </c>
       <c r="AK2" t="n">
-        <v>9.350059737102587</v>
+        <v>0.06975940676160697</v>
       </c>
       <c r="AL2" t="n">
-        <v>8.284036678757811</v>
+        <v>-0.1966980979037443</v>
       </c>
       <c r="AM2" t="n">
-        <v>17.73559584672712</v>
+        <v>1.020935718344646</v>
       </c>
       <c r="AN2" t="n">
-        <v>15.05756921512721</v>
+        <v>-0.3672104789285591</v>
       </c>
       <c r="AO2" t="n">
-        <v>16.38526148905168</v>
+        <v>0.9805686544273691</v>
       </c>
       <c r="AP2" t="n">
-        <v>10.44498606567276</v>
+        <v>-1.743631025432441</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.08794480290338</v>
+        <v>1.442397233308467</v>
       </c>
       <c r="AR2" t="n">
-        <v>18.68527777588395</v>
+        <v>-0.3145371740523242</v>
       </c>
       <c r="AS2" t="n">
-        <v>22.09372264574459</v>
+        <v>-3.528750452680285</v>
       </c>
       <c r="AT2" t="n">
-        <v>12.78489466801624</v>
+        <v>0.8478028813039451</v>
       </c>
     </row>
     <row r="3">
@@ -2200,139 +2200,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.66966806836041</v>
+        <v>-1.383951582802387</v>
       </c>
       <c r="C3" t="n">
-        <v>9.881324912847749</v>
+        <v>-0.553044355374757</v>
       </c>
       <c r="D3" t="n">
-        <v>20.67133450524295</v>
+        <v>-1.12710842046091</v>
       </c>
       <c r="E3" t="n">
-        <v>13.97405571157345</v>
+        <v>-0.1228471864979781</v>
       </c>
       <c r="F3" t="n">
-        <v>20.957763493935</v>
+        <v>-6.141581784726942</v>
       </c>
       <c r="G3" t="n">
-        <v>17.20503641658092</v>
+        <v>-2.20113107416697</v>
       </c>
       <c r="H3" t="n">
-        <v>18.37063528893662</v>
+        <v>-2.29609477239201</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5325976509741</v>
+        <v>-11.06506753838849</v>
       </c>
       <c r="J3" t="n">
-        <v>6.134101044130142</v>
+        <v>0.321314892326038</v>
       </c>
       <c r="K3" t="n">
-        <v>16.31918675138066</v>
+        <v>0.2860379815195486</v>
       </c>
       <c r="L3" t="n">
-        <v>19.36687092269202</v>
+        <v>-2.228889848678961</v>
       </c>
       <c r="M3" t="n">
-        <v>19.9087210634161</v>
+        <v>-0.9377542043709042</v>
       </c>
       <c r="N3" t="n">
-        <v>14.6683635438186</v>
+        <v>-1.321559440659771</v>
       </c>
       <c r="O3" t="n">
-        <v>11.38493707714738</v>
+        <v>-1.882450344503694</v>
       </c>
       <c r="P3" t="n">
-        <v>22.71230479728805</v>
+        <v>-1.297252992049994</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.78124748820939</v>
+        <v>-1.854270530534729</v>
       </c>
       <c r="R3" t="n">
-        <v>15.99777145287985</v>
+        <v>-1.408563783887963</v>
       </c>
       <c r="S3" t="n">
-        <v>16.55058698396441</v>
+        <v>-1.841437995028841</v>
       </c>
       <c r="T3" t="n">
-        <v>20.91160786757982</v>
+        <v>-0.6615828754436208</v>
       </c>
       <c r="U3" t="n">
-        <v>10.9584689646352</v>
+        <v>-3.550621437694598</v>
       </c>
       <c r="V3" t="n">
-        <v>5.079402345820294</v>
+        <v>0.4906128714349158</v>
       </c>
       <c r="W3" t="n">
-        <v>14.65388207626278</v>
+        <v>-0.351490546593082</v>
       </c>
       <c r="X3" t="n">
-        <v>11.99701106241501</v>
+        <v>0.3832866236073409</v>
       </c>
       <c r="Y3" t="n">
-        <v>18.85454770446196</v>
+        <v>-1.743849390593741</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.50251117764969</v>
+        <v>-0.5935039611675634</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.395458496288052</v>
+        <v>0.5899094216351255</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.8606998072146</v>
+        <v>-1.942600235235783</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.64813133984202</v>
+        <v>-0.6439579658690491</v>
       </c>
       <c r="AD3" t="n">
-        <v>14.01267001301277</v>
+        <v>0.2495532155109554</v>
       </c>
       <c r="AE3" t="n">
-        <v>18.12061637209431</v>
+        <v>0.2177356350895838</v>
       </c>
       <c r="AF3" t="n">
-        <v>14.9660749514917</v>
+        <v>-2.005842268150364</v>
       </c>
       <c r="AG3" t="n">
-        <v>13.0313326060332</v>
+        <v>-1.590176542716117</v>
       </c>
       <c r="AH3" t="n">
-        <v>19.33240797705709</v>
+        <v>-3.598433976219468</v>
       </c>
       <c r="AI3" t="n">
-        <v>14.84501400289153</v>
+        <v>-0.1634545478121829</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9.329100541370561</v>
+        <v>-0.218630347393141</v>
       </c>
       <c r="AK3" t="n">
-        <v>8.867458764442215</v>
+        <v>-0.8529021301082969</v>
       </c>
       <c r="AL3" t="n">
-        <v>8.919861141425528</v>
+        <v>-0.3916266153978345</v>
       </c>
       <c r="AM3" t="n">
-        <v>17.21627848096804</v>
+        <v>-0.400273626177329</v>
       </c>
       <c r="AN3" t="n">
-        <v>13.07395706029272</v>
+        <v>-2.66900991564094</v>
       </c>
       <c r="AO3" t="n">
-        <v>17.43624095525147</v>
+        <v>0.9176843807737338</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.791163996665368</v>
+        <v>-1.761209348036886</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.24184527187982</v>
+        <v>-1.037752083447696</v>
       </c>
       <c r="AR3" t="n">
-        <v>16.8511489997417</v>
+        <v>-1.232755257860207</v>
       </c>
       <c r="AS3" t="n">
-        <v>20.6836532938557</v>
+        <v>-2.669007408631948</v>
       </c>
       <c r="AT3" t="n">
-        <v>13.46801063219757</v>
+        <v>0.007730086710470374</v>
       </c>
     </row>
   </sheetData>
